--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA331"/>
+  <dimension ref="A1:AA333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -34776,6 +34776,220 @@
       </c>
       <c r="AA331" s="2" t="inlineStr"/>
     </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>27144</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>Ružomberok</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>Štiavnická cesta</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>034 01</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>https://dozsa.sk</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr"/>
+      <c r="K332" s="2" t="inlineStr"/>
+      <c r="L332" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>eshop@dozsa.sk</t>
+        </is>
+      </c>
+      <c r="O332" s="2" t="inlineStr"/>
+      <c r="P332" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>36419575</t>
+        </is>
+      </c>
+      <c r="R332" s="2" t="inlineStr"/>
+      <c r="S332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="T332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="U332" s="2" t="inlineStr"/>
+      <c r="V332" s="2" t="inlineStr"/>
+      <c r="W332" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Šimko</t>
+        </is>
+      </c>
+      <c r="X332" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y332" s="2" t="inlineStr"/>
+      <c r="Z332" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miroslav-%c5%a1imko-29229a68/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>27144</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>Ružomberok</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>Štiavnická cesta</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>034 01</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>https://dozsa.sk</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr"/>
+      <c r="K333" s="2" t="inlineStr"/>
+      <c r="L333" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N333" s="2" t="inlineStr">
+        <is>
+          <t>eshop@dozsa.sk</t>
+        </is>
+      </c>
+      <c r="O333" s="2" t="inlineStr"/>
+      <c r="P333" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>36419575</t>
+        </is>
+      </c>
+      <c r="R333" s="2" t="inlineStr"/>
+      <c r="S333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="T333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="U333" s="2" t="inlineStr"/>
+      <c r="V333" s="2" t="inlineStr"/>
+      <c r="W333" s="2" t="inlineStr">
+        <is>
+          <t>Vladimír Drengubiak</t>
+        </is>
+      </c>
+      <c r="X333" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y333" s="2" t="inlineStr"/>
+      <c r="Z333" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA333" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA333"/>
+  <dimension ref="A1:AA335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -34990,6 +34990,220 @@
       </c>
       <c r="AA333" s="2" t="inlineStr"/>
     </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>27144</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>Ružomberok</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>Štiavnická cesta</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>034 01</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>https://dozsa.sk</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr"/>
+      <c r="K334" s="2" t="inlineStr"/>
+      <c r="L334" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M334" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N334" s="2" t="inlineStr">
+        <is>
+          <t>eshop@dozsa.sk</t>
+        </is>
+      </c>
+      <c r="O334" s="2" t="inlineStr"/>
+      <c r="P334" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q334" s="2" t="inlineStr">
+        <is>
+          <t>36419575</t>
+        </is>
+      </c>
+      <c r="R334" s="2" t="inlineStr"/>
+      <c r="S334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="T334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="U334" s="2" t="inlineStr"/>
+      <c r="V334" s="2" t="inlineStr"/>
+      <c r="W334" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Šimko</t>
+        </is>
+      </c>
+      <c r="X334" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y334" s="2" t="inlineStr"/>
+      <c r="Z334" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miroslav-%c5%a1imko-29229a68/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>27144</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>Ružomberok</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>Štiavnická cesta</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>034 01</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>https://dozsa.sk</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr"/>
+      <c r="K335" s="2" t="inlineStr"/>
+      <c r="L335" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M335" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N335" s="2" t="inlineStr">
+        <is>
+          <t>eshop@dozsa.sk</t>
+        </is>
+      </c>
+      <c r="O335" s="2" t="inlineStr"/>
+      <c r="P335" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>36419575</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="inlineStr"/>
+      <c r="S335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="T335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="U335" s="2" t="inlineStr"/>
+      <c r="V335" s="2" t="inlineStr"/>
+      <c r="W335" s="2" t="inlineStr">
+        <is>
+          <t>Vladimír Drengubiak</t>
+        </is>
+      </c>
+      <c r="X335" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y335" s="2" t="inlineStr"/>
+      <c r="Z335" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA335" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA335"/>
+  <dimension ref="A1:AA337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -35204,6 +35204,220 @@
       </c>
       <c r="AA335" s="2" t="inlineStr"/>
     </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>27144</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>Ružomberok</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>Štiavnická cesta</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>034 01</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>https://dozsa.sk</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr"/>
+      <c r="K336" s="2" t="inlineStr"/>
+      <c r="L336" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M336" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N336" s="2" t="inlineStr">
+        <is>
+          <t>eshop@dozsa.sk</t>
+        </is>
+      </c>
+      <c r="O336" s="2" t="inlineStr"/>
+      <c r="P336" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q336" s="2" t="inlineStr">
+        <is>
+          <t>36419575</t>
+        </is>
+      </c>
+      <c r="R336" s="2" t="inlineStr"/>
+      <c r="S336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="T336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="U336" s="2" t="inlineStr"/>
+      <c r="V336" s="2" t="inlineStr"/>
+      <c r="W336" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Šimko</t>
+        </is>
+      </c>
+      <c r="X336" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y336" s="2" t="inlineStr"/>
+      <c r="Z336" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miroslav-%c5%a1imko-29229a68/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>27144</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>Ružomberok</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>Štiavnická cesta</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>034 01</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>https://dozsa.sk</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr"/>
+      <c r="K337" s="2" t="inlineStr"/>
+      <c r="L337" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M337" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N337" s="2" t="inlineStr">
+        <is>
+          <t>eshop@dozsa.sk</t>
+        </is>
+      </c>
+      <c r="O337" s="2" t="inlineStr"/>
+      <c r="P337" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q337" s="2" t="inlineStr">
+        <is>
+          <t>36419575</t>
+        </is>
+      </c>
+      <c r="R337" s="2" t="inlineStr"/>
+      <c r="S337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="T337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="U337" s="2" t="inlineStr"/>
+      <c r="V337" s="2" t="inlineStr"/>
+      <c r="W337" s="2" t="inlineStr">
+        <is>
+          <t>Vladimír Drengubiak</t>
+        </is>
+      </c>
+      <c r="X337" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y337" s="2" t="inlineStr"/>
+      <c r="Z337" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA337" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA337"/>
+  <dimension ref="A1:AA341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -35418,6 +35418,410 @@
       </c>
       <c r="AA337" s="2" t="inlineStr"/>
     </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>Kapka Wina</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>Kapka Wina</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>58801</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>Bielsko-Biała</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>Województwo Śląskie</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>5 Widok</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>43-300</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>https://kapkawina.pl</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr"/>
+      <c r="K338" s="2" t="inlineStr"/>
+      <c r="L338" s="2" t="inlineStr"/>
+      <c r="M338" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N338" s="2" t="inlineStr">
+        <is>
+          <t>info@kapkawina.pl</t>
+        </is>
+      </c>
+      <c r="O338" s="2" t="inlineStr"/>
+      <c r="P338" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q338" s="2" t="inlineStr"/>
+      <c r="R338" s="2" t="inlineStr"/>
+      <c r="S338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KapkaWina/</t>
+        </is>
+      </c>
+      <c r="T338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kapkawina_zywiec/</t>
+        </is>
+      </c>
+      <c r="U338" s="2" t="inlineStr"/>
+      <c r="V338" s="2" t="inlineStr"/>
+      <c r="W338" s="2" t="inlineStr">
+        <is>
+          <t>Petr Kaspřák</t>
+        </is>
+      </c>
+      <c r="X338" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y338" s="2" t="inlineStr"/>
+      <c r="Z338" s="2" t="inlineStr"/>
+      <c r="AA338" s="2" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>Kapka Wina</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>Kapka Wina</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>58801</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>Bielsko-Biała</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Województwo Śląskie</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>5 Widok</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>43-300</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>https://kapkawina.pl</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr"/>
+      <c r="K339" s="2" t="inlineStr"/>
+      <c r="L339" s="2" t="inlineStr"/>
+      <c r="M339" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N339" s="2" t="inlineStr">
+        <is>
+          <t>info@kapkawina.pl</t>
+        </is>
+      </c>
+      <c r="O339" s="2" t="inlineStr"/>
+      <c r="P339" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q339" s="2" t="inlineStr"/>
+      <c r="R339" s="2" t="inlineStr"/>
+      <c r="S339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KapkaWina/</t>
+        </is>
+      </c>
+      <c r="T339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kapkawina_zywiec/</t>
+        </is>
+      </c>
+      <c r="U339" s="2" t="inlineStr"/>
+      <c r="V339" s="2" t="inlineStr"/>
+      <c r="W339" s="2" t="inlineStr">
+        <is>
+          <t>Hubert Rodak</t>
+        </is>
+      </c>
+      <c r="X339" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y339" s="2" t="inlineStr"/>
+      <c r="Z339" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA339" s="2" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>27144</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>Ružomberok</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>Štiavnická cesta</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>034 01</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>https://dozsa.sk</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr"/>
+      <c r="K340" s="2" t="inlineStr"/>
+      <c r="L340" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M340" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N340" s="2" t="inlineStr">
+        <is>
+          <t>eshop@dozsa.sk</t>
+        </is>
+      </c>
+      <c r="O340" s="2" t="inlineStr"/>
+      <c r="P340" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q340" s="2" t="inlineStr">
+        <is>
+          <t>36419575</t>
+        </is>
+      </c>
+      <c r="R340" s="2" t="inlineStr"/>
+      <c r="S340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="T340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="U340" s="2" t="inlineStr"/>
+      <c r="V340" s="2" t="inlineStr"/>
+      <c r="W340" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Šimko</t>
+        </is>
+      </c>
+      <c r="X340" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y340" s="2" t="inlineStr"/>
+      <c r="Z340" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miroslav-%c5%a1imko-29229a68/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>Dozsa, Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>27144</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>Ružomberok</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>Štiavnická cesta</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>034 01</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>https://dozsa.sk</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr"/>
+      <c r="K341" s="2" t="inlineStr"/>
+      <c r="L341" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M341" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N341" s="2" t="inlineStr">
+        <is>
+          <t>eshop@dozsa.sk</t>
+        </is>
+      </c>
+      <c r="O341" s="2" t="inlineStr"/>
+      <c r="P341" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q341" s="2" t="inlineStr">
+        <is>
+          <t>36419575</t>
+        </is>
+      </c>
+      <c r="R341" s="2" t="inlineStr"/>
+      <c r="S341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="T341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dozsa.sk/</t>
+        </is>
+      </c>
+      <c r="U341" s="2" t="inlineStr"/>
+      <c r="V341" s="2" t="inlineStr"/>
+      <c r="W341" s="2" t="inlineStr">
+        <is>
+          <t>Vladimír Drengubiak</t>
+        </is>
+      </c>
+      <c r="X341" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y341" s="2" t="inlineStr"/>
+      <c r="Z341" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA341" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA341"/>
+  <dimension ref="A1:AA342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -35822,6 +35822,99 @@
       </c>
       <c r="AA341" s="2" t="inlineStr"/>
     </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Ilt Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>Ilt Spol. S R.o.</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>11883</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>9 Stromová</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>831 01</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vina-sveta.sk</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr"/>
+      <c r="K342" s="2" t="inlineStr"/>
+      <c r="L342" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M342" s="2" t="inlineStr"/>
+      <c r="N342" s="2" t="inlineStr">
+        <is>
+          <t>info@vina-sveta.sk</t>
+        </is>
+      </c>
+      <c r="O342" s="2" t="inlineStr"/>
+      <c r="P342" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q342" s="2" t="inlineStr">
+        <is>
+          <t>35855827</t>
+        </is>
+      </c>
+      <c r="R342" s="2" t="inlineStr"/>
+      <c r="S342" s="2" t="inlineStr"/>
+      <c r="T342" s="2" t="inlineStr"/>
+      <c r="U342" s="2" t="inlineStr"/>
+      <c r="V342" s="2" t="inlineStr"/>
+      <c r="W342" s="2" t="inlineStr">
+        <is>
+          <t>Ivan Lacko</t>
+        </is>
+      </c>
+      <c r="X342" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y342" s="2" t="inlineStr"/>
+      <c r="Z342" s="2" t="inlineStr"/>
+      <c r="AA342" s="2" t="inlineStr">
+        <is>
+          <t>https://sk.linkedin.com/in/ivan-lacko-814261b</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA342"/>
+  <dimension ref="A1:AA343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -35915,6 +35915,103 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>Eurotrade Business Services Ltd.</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>Eurotrade Business Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>82260</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>23 Royova</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>831 01</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>http://www.ebs.sk</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr"/>
+      <c r="K343" s="2" t="inlineStr"/>
+      <c r="L343" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M343" s="2" t="inlineStr"/>
+      <c r="N343" s="2" t="inlineStr">
+        <is>
+          <t>eurotrade@ebs.sk</t>
+        </is>
+      </c>
+      <c r="O343" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/654 571 29</t>
+        </is>
+      </c>
+      <c r="P343" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q343" s="2" t="inlineStr">
+        <is>
+          <t>35866845</t>
+        </is>
+      </c>
+      <c r="R343" s="2" t="inlineStr"/>
+      <c r="S343" s="2" t="inlineStr"/>
+      <c r="T343" s="2" t="inlineStr"/>
+      <c r="U343" s="2" t="inlineStr"/>
+      <c r="V343" s="2" t="inlineStr"/>
+      <c r="W343" s="2" t="inlineStr">
+        <is>
+          <t>Juraj Hanus</t>
+        </is>
+      </c>
+      <c r="X343" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y343" s="2" t="inlineStr"/>
+      <c r="Z343" s="2" t="inlineStr"/>
+      <c r="AA343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/juraj-hanus-92716b90/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA343"/>
+  <dimension ref="A1:AA344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -36012,6 +36012,103 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>Eurotrade Business Services Ltd.</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>Eurotrade Business Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>82260</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>23 Royova</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>831 01</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>http://www.ebs.sk</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr"/>
+      <c r="K344" s="2" t="inlineStr"/>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr"/>
+      <c r="N344" s="2" t="inlineStr">
+        <is>
+          <t>eurotrade@ebs.sk</t>
+        </is>
+      </c>
+      <c r="O344" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/654 571 29</t>
+        </is>
+      </c>
+      <c r="P344" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q344" s="2" t="inlineStr">
+        <is>
+          <t>35866845</t>
+        </is>
+      </c>
+      <c r="R344" s="2" t="inlineStr"/>
+      <c r="S344" s="2" t="inlineStr"/>
+      <c r="T344" s="2" t="inlineStr"/>
+      <c r="U344" s="2" t="inlineStr"/>
+      <c r="V344" s="2" t="inlineStr"/>
+      <c r="W344" s="2" t="inlineStr">
+        <is>
+          <t>Juraj Hanus</t>
+        </is>
+      </c>
+      <c r="X344" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y344" s="2" t="inlineStr"/>
+      <c r="Z344" s="2" t="inlineStr"/>
+      <c r="AA344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/juraj-hanus-92716b90/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA344"/>
+  <dimension ref="A1:AA356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -36109,6 +36109,1174 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>Kika Bier, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>Kika Bier, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>19466</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>Žilina</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>Brodno 81</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>010 14</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kikabier.sk</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr"/>
+      <c r="K345" s="2" t="inlineStr"/>
+      <c r="L345" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="inlineStr"/>
+      <c r="N345" s="2" t="inlineStr">
+        <is>
+          <t>kikabier@post.sk</t>
+        </is>
+      </c>
+      <c r="O345" s="2" t="inlineStr">
+        <is>
+          <t>+421 41/596 20 70</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>36688461</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="inlineStr"/>
+      <c r="S345" s="2" t="inlineStr"/>
+      <c r="T345" s="2" t="inlineStr"/>
+      <c r="U345" s="2" t="inlineStr"/>
+      <c r="V345" s="2" t="inlineStr"/>
+      <c r="W345" s="2" t="inlineStr"/>
+      <c r="X345" s="2" t="inlineStr"/>
+      <c r="Y345" s="2" t="inlineStr"/>
+      <c r="Z345" s="2" t="inlineStr"/>
+      <c r="AA345" s="2" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>Julk S.r.o.</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>Julk S.r.o.</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>43792</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>Vysoká pri Morave</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Malacky</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>260, 10 Družstevná</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>900 66</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.julk.sk</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr"/>
+      <c r="K346" s="2" t="inlineStr"/>
+      <c r="L346" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="inlineStr"/>
+      <c r="N346" s="2" t="inlineStr">
+        <is>
+          <t>office@julk.sk</t>
+        </is>
+      </c>
+      <c r="O346" s="2" t="inlineStr"/>
+      <c r="P346" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q346" s="2" t="inlineStr">
+        <is>
+          <t>47436981</t>
+        </is>
+      </c>
+      <c r="R346" s="2" t="inlineStr"/>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/julk_international_wines/100027452033991/</t>
+        </is>
+      </c>
+      <c r="T346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/julk_international_wines/</t>
+        </is>
+      </c>
+      <c r="U346" s="2" t="inlineStr"/>
+      <c r="V346" s="2" t="inlineStr"/>
+      <c r="W346" s="2" t="inlineStr">
+        <is>
+          <t>Milan Jurík</t>
+        </is>
+      </c>
+      <c r="X346" s="2" t="inlineStr">
+        <is>
+          <t>Sales/ Distribution</t>
+        </is>
+      </c>
+      <c r="Y346" s="2" t="inlineStr"/>
+      <c r="Z346" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA346" s="2" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>Julk S.r.o.</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Julk S.r.o.</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>43792</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>Vysoká pri Morave</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Malacky</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>260, 10 Družstevná</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>900 66</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.julk.sk</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr"/>
+      <c r="K347" s="2" t="inlineStr"/>
+      <c r="L347" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="inlineStr"/>
+      <c r="N347" s="2" t="inlineStr">
+        <is>
+          <t>office@julk.sk</t>
+        </is>
+      </c>
+      <c r="O347" s="2" t="inlineStr"/>
+      <c r="P347" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q347" s="2" t="inlineStr">
+        <is>
+          <t>47436981</t>
+        </is>
+      </c>
+      <c r="R347" s="2" t="inlineStr"/>
+      <c r="S347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/julk_international_wines/100027452033991/</t>
+        </is>
+      </c>
+      <c r="T347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/julk_international_wines/</t>
+        </is>
+      </c>
+      <c r="U347" s="2" t="inlineStr"/>
+      <c r="V347" s="2" t="inlineStr"/>
+      <c r="W347" s="2" t="inlineStr">
+        <is>
+          <t>Lukáš Jurík</t>
+        </is>
+      </c>
+      <c r="X347" s="2" t="inlineStr">
+        <is>
+          <t>Consultant For Companies And Gastronomy</t>
+        </is>
+      </c>
+      <c r="Y347" s="2" t="inlineStr"/>
+      <c r="Z347" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA347" s="2" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>Zlatý Vinic S.r.o.</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>Zlatý Vinic S.r.o.</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>53803</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>23 Zvolenská cesta</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>974 01</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zlatyvinic.eu</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr"/>
+      <c r="K348" s="2" t="inlineStr"/>
+      <c r="L348" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="inlineStr"/>
+      <c r="N348" s="2" t="inlineStr">
+        <is>
+          <t>eshop@zlatyvinic.eu</t>
+        </is>
+      </c>
+      <c r="O348" s="2" t="inlineStr"/>
+      <c r="P348" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q348" s="2" t="inlineStr">
+        <is>
+          <t>36838021</t>
+        </is>
+      </c>
+      <c r="R348" s="2" t="inlineStr"/>
+      <c r="S348" s="2" t="inlineStr"/>
+      <c r="T348" s="2" t="inlineStr"/>
+      <c r="U348" s="2" t="inlineStr"/>
+      <c r="V348" s="2" t="inlineStr"/>
+      <c r="W348" s="2" t="inlineStr"/>
+      <c r="X348" s="2" t="inlineStr"/>
+      <c r="Y348" s="2" t="inlineStr"/>
+      <c r="Z348" s="2" t="inlineStr"/>
+      <c r="AA348" s="2" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>146391</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>2321, 71 Piešťanská</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.sk</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr"/>
+      <c r="K349" s="2" t="inlineStr"/>
+      <c r="L349" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="inlineStr"/>
+      <c r="N349" s="2" t="inlineStr">
+        <is>
+          <t>info@bidfood.sk</t>
+        </is>
+      </c>
+      <c r="O349" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/774 28 11</t>
+        </is>
+      </c>
+      <c r="P349" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q349" s="2" t="inlineStr">
+        <is>
+          <t>34152199</t>
+        </is>
+      </c>
+      <c r="R349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bidfood-slovakia/</t>
+        </is>
+      </c>
+      <c r="S349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfood.sk</t>
+        </is>
+      </c>
+      <c r="T349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfood_slovakia</t>
+        </is>
+      </c>
+      <c r="U349" s="2" t="inlineStr"/>
+      <c r="V349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@bidfoodslovakias.r.o.8178</t>
+        </is>
+      </c>
+      <c r="W349" s="2" t="inlineStr">
+        <is>
+          <t>Tomáš Psota</t>
+        </is>
+      </c>
+      <c r="X349" s="2" t="inlineStr">
+        <is>
+          <t>Purchase Director</t>
+        </is>
+      </c>
+      <c r="Y349" s="2" t="inlineStr"/>
+      <c r="Z349" s="2" t="inlineStr"/>
+      <c r="AA349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tom%C3%A1%C5%A1-psota-20122b295/</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>146391</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>2321, 71 Piešťanská</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.sk</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr"/>
+      <c r="K350" s="2" t="inlineStr"/>
+      <c r="L350" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="inlineStr"/>
+      <c r="N350" s="2" t="inlineStr">
+        <is>
+          <t>info@bidfood.sk</t>
+        </is>
+      </c>
+      <c r="O350" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/774 28 11</t>
+        </is>
+      </c>
+      <c r="P350" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q350" s="2" t="inlineStr">
+        <is>
+          <t>34152199</t>
+        </is>
+      </c>
+      <c r="R350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bidfood-slovakia/</t>
+        </is>
+      </c>
+      <c r="S350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfood.sk</t>
+        </is>
+      </c>
+      <c r="T350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfood_slovakia</t>
+        </is>
+      </c>
+      <c r="U350" s="2" t="inlineStr"/>
+      <c r="V350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@bidfoodslovakias.r.o.8178</t>
+        </is>
+      </c>
+      <c r="W350" s="2" t="inlineStr">
+        <is>
+          <t>Peter Slobodnik</t>
+        </is>
+      </c>
+      <c r="X350" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y350" s="2" t="inlineStr"/>
+      <c r="Z350" s="2" t="inlineStr"/>
+      <c r="AA350" s="2" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>146391</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>2321, 71 Piešťanská</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.sk</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="inlineStr"/>
+      <c r="K351" s="2" t="inlineStr"/>
+      <c r="L351" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="M351" s="2" t="inlineStr"/>
+      <c r="N351" s="2" t="inlineStr">
+        <is>
+          <t>info@bidfood.sk</t>
+        </is>
+      </c>
+      <c r="O351" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/774 28 11</t>
+        </is>
+      </c>
+      <c r="P351" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q351" s="2" t="inlineStr">
+        <is>
+          <t>34152199</t>
+        </is>
+      </c>
+      <c r="R351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bidfood-slovakia/</t>
+        </is>
+      </c>
+      <c r="S351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfood.sk</t>
+        </is>
+      </c>
+      <c r="T351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfood_slovakia</t>
+        </is>
+      </c>
+      <c r="U351" s="2" t="inlineStr"/>
+      <c r="V351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@bidfoodslovakias.r.o.8178</t>
+        </is>
+      </c>
+      <c r="W351" s="2" t="inlineStr">
+        <is>
+          <t>Peter Kadash</t>
+        </is>
+      </c>
+      <c r="X351" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y351" s="2" t="inlineStr"/>
+      <c r="Z351" s="2" t="inlineStr"/>
+      <c r="AA351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-kad%C3%A1%C5%A1-951909147/</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>Coop Jednota Cadca, Spotrebné Družstvo</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>Coop Jednota Cadca, Spotrebné Družstvo</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>146368</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>Čadca</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>87, 32 Palárikova</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>022 01</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>http://www.coopcadca.sk</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr"/>
+      <c r="K352" s="2" t="inlineStr"/>
+      <c r="L352" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="M352" s="2" t="inlineStr"/>
+      <c r="N352" s="2" t="inlineStr">
+        <is>
+          <t>informacie@ca.coop.sk</t>
+        </is>
+      </c>
+      <c r="O352" s="2" t="inlineStr">
+        <is>
+          <t>+421 41/433 21 55</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="Q352" s="2" t="inlineStr">
+        <is>
+          <t>00168947</t>
+        </is>
+      </c>
+      <c r="R352" s="2" t="inlineStr"/>
+      <c r="S352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CJCadca</t>
+        </is>
+      </c>
+      <c r="T352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coop_jednota</t>
+        </is>
+      </c>
+      <c r="U352" s="2" t="inlineStr"/>
+      <c r="V352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@COOPJednotaSlovensko</t>
+        </is>
+      </c>
+      <c r="W352" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Janík</t>
+        </is>
+      </c>
+      <c r="X352" s="2" t="inlineStr">
+        <is>
+          <t>Chairman Of The Board Of Directors</t>
+        </is>
+      </c>
+      <c r="Y352" s="2" t="inlineStr"/>
+      <c r="Z352" s="2" t="inlineStr"/>
+      <c r="AA352" s="2" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>Coop Jednota Cadca, Spotrebné Družstvo</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>Coop Jednota Cadca, Spotrebné Družstvo</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>146368</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>Čadca</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>87, 32 Palárikova</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>022 01</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>http://www.coopcadca.sk</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="inlineStr"/>
+      <c r="K353" s="2" t="inlineStr"/>
+      <c r="L353" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="inlineStr"/>
+      <c r="N353" s="2" t="inlineStr">
+        <is>
+          <t>informacie@ca.coop.sk</t>
+        </is>
+      </c>
+      <c r="O353" s="2" t="inlineStr">
+        <is>
+          <t>+421 41/433 21 55</t>
+        </is>
+      </c>
+      <c r="P353" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="Q353" s="2" t="inlineStr">
+        <is>
+          <t>00168947</t>
+        </is>
+      </c>
+      <c r="R353" s="2" t="inlineStr"/>
+      <c r="S353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CJCadca</t>
+        </is>
+      </c>
+      <c r="T353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coop_jednota</t>
+        </is>
+      </c>
+      <c r="U353" s="2" t="inlineStr"/>
+      <c r="V353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@COOPJednotaSlovensko</t>
+        </is>
+      </c>
+      <c r="W353" s="2" t="inlineStr">
+        <is>
+          <t>Bohuslav Cyprich</t>
+        </is>
+      </c>
+      <c r="X353" s="2" t="inlineStr">
+        <is>
+          <t>Vice Chairman Of The Board Of Directors</t>
+        </is>
+      </c>
+      <c r="Y353" s="2" t="inlineStr"/>
+      <c r="Z353" s="2" t="inlineStr"/>
+      <c r="AA353" s="2" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>Infotex, Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>Infotex, Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>24829</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava II</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>8052, 78 Hradská</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>821 07</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr"/>
+      <c r="J354" s="2" t="inlineStr"/>
+      <c r="K354" s="2" t="inlineStr"/>
+      <c r="L354" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="inlineStr"/>
+      <c r="N354" s="2" t="inlineStr">
+        <is>
+          <t>info@inmedio.sk</t>
+        </is>
+      </c>
+      <c r="O354" s="2" t="inlineStr"/>
+      <c r="P354" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q354" s="2" t="inlineStr">
+        <is>
+          <t>35753692</t>
+        </is>
+      </c>
+      <c r="R354" s="2" t="inlineStr"/>
+      <c r="S354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/eshop.inmedio/</t>
+        </is>
+      </c>
+      <c r="T354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/in_medio/</t>
+        </is>
+      </c>
+      <c r="U354" s="2" t="inlineStr"/>
+      <c r="V354" s="2" t="inlineStr"/>
+      <c r="W354" s="2" t="inlineStr"/>
+      <c r="X354" s="2" t="inlineStr"/>
+      <c r="Y354" s="2" t="inlineStr"/>
+      <c r="Z354" s="2" t="inlineStr"/>
+      <c r="AA354" s="2" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>100yards &amp; Spirits, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>100yards &amp; Spirits, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>158583</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>2946, 19 Na Revíne</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>831 01</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinohlad.sk</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr"/>
+      <c r="K355" s="2" t="inlineStr"/>
+      <c r="L355" s="2" t="inlineStr"/>
+      <c r="M355" s="2" t="inlineStr"/>
+      <c r="N355" s="2" t="inlineStr">
+        <is>
+          <t>vyriesime@vinohlad.sk</t>
+        </is>
+      </c>
+      <c r="O355" s="2" t="inlineStr"/>
+      <c r="P355" s="2" t="inlineStr"/>
+      <c r="Q355" s="2" t="inlineStr"/>
+      <c r="R355" s="2" t="inlineStr"/>
+      <c r="S355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinonastanicke/</t>
+        </is>
+      </c>
+      <c r="T355" s="2" t="inlineStr"/>
+      <c r="U355" s="2" t="inlineStr"/>
+      <c r="V355" s="2" t="inlineStr"/>
+      <c r="W355" s="2" t="inlineStr"/>
+      <c r="X355" s="2" t="inlineStr"/>
+      <c r="Y355" s="2" t="inlineStr"/>
+      <c r="Z355" s="2" t="inlineStr"/>
+      <c r="AA355" s="2" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>Eurotrade Business Services Ltd.</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>Eurotrade Business Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>82260</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>23 Royova</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>831 01</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>http://www.ebs.sk</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr"/>
+      <c r="K356" s="2" t="inlineStr"/>
+      <c r="L356" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="inlineStr"/>
+      <c r="N356" s="2" t="inlineStr">
+        <is>
+          <t>eurotrade@ebs.sk</t>
+        </is>
+      </c>
+      <c r="O356" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/654 571 29</t>
+        </is>
+      </c>
+      <c r="P356" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q356" s="2" t="inlineStr">
+        <is>
+          <t>35866845</t>
+        </is>
+      </c>
+      <c r="R356" s="2" t="inlineStr"/>
+      <c r="S356" s="2" t="inlineStr"/>
+      <c r="T356" s="2" t="inlineStr"/>
+      <c r="U356" s="2" t="inlineStr"/>
+      <c r="V356" s="2" t="inlineStr"/>
+      <c r="W356" s="2" t="inlineStr">
+        <is>
+          <t>Juraj Hanus</t>
+        </is>
+      </c>
+      <c r="X356" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y356" s="2" t="inlineStr"/>
+      <c r="Z356" s="2" t="inlineStr"/>
+      <c r="AA356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/juraj-hanus-92716b90/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA356"/>
+  <dimension ref="A1:AA400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -37277,6 +37277,3558 @@
         </is>
       </c>
     </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>Selaví s.r.o.</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr"/>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>168466</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>Svätý Jur</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>Prostredná 13/49</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>900 21</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>https://eshop.viajur.sk</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr"/>
+      <c r="K357" s="2" t="inlineStr"/>
+      <c r="L357" s="2" t="inlineStr"/>
+      <c r="M357" s="2" t="inlineStr"/>
+      <c r="N357" s="2" t="inlineStr">
+        <is>
+          <t>info@viajur.sk</t>
+        </is>
+      </c>
+      <c r="O357" s="2" t="inlineStr"/>
+      <c r="P357" s="2" t="inlineStr"/>
+      <c r="Q357" s="2" t="inlineStr"/>
+      <c r="R357" s="2" t="inlineStr"/>
+      <c r="S357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viajur/?locale=sk_SK</t>
+        </is>
+      </c>
+      <c r="T357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viajursk/</t>
+        </is>
+      </c>
+      <c r="U357" s="2" t="inlineStr"/>
+      <c r="V357" s="2" t="inlineStr"/>
+      <c r="W357" s="2" t="inlineStr"/>
+      <c r="X357" s="2" t="inlineStr"/>
+      <c r="Y357" s="2" t="inlineStr"/>
+      <c r="Z357" s="2" t="inlineStr"/>
+      <c r="AA357" s="2" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>Vinimp s.r.o.</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr"/>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>168464</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>Dunajská Streda</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>Trnava</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>Športová 5848/72A</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>929 01</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinimp.sk</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr"/>
+      <c r="K358" s="2" t="inlineStr"/>
+      <c r="L358" s="2" t="inlineStr"/>
+      <c r="M358" s="2" t="inlineStr"/>
+      <c r="N358" s="2" t="inlineStr">
+        <is>
+          <t>vinimp@vinimp.sk</t>
+        </is>
+      </c>
+      <c r="O358" s="2" t="inlineStr"/>
+      <c r="P358" s="2" t="inlineStr"/>
+      <c r="Q358" s="2" t="inlineStr"/>
+      <c r="R358" s="2" t="inlineStr"/>
+      <c r="S358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vinarium-Vinimp-sro-2005664886393707/</t>
+        </is>
+      </c>
+      <c r="T358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinarium.ds/</t>
+        </is>
+      </c>
+      <c r="U358" s="2" t="inlineStr"/>
+      <c r="V358" s="2" t="inlineStr"/>
+      <c r="W358" s="2" t="inlineStr"/>
+      <c r="X358" s="2" t="inlineStr"/>
+      <c r="Y358" s="2" t="inlineStr"/>
+      <c r="Z358" s="2" t="inlineStr"/>
+      <c r="AA358" s="2" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>WALPER DRINKS, s.r.o.</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr"/>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>168462</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>Turbínová 11</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>83104</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.walperdrinks.sk</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr"/>
+      <c r="K359" s="2" t="inlineStr"/>
+      <c r="L359" s="2" t="inlineStr"/>
+      <c r="M359" s="2" t="inlineStr"/>
+      <c r="N359" s="2" t="inlineStr">
+        <is>
+          <t>info@walperdrinks.sk</t>
+        </is>
+      </c>
+      <c r="O359" s="2" t="inlineStr"/>
+      <c r="P359" s="2" t="inlineStr"/>
+      <c r="Q359" s="2" t="inlineStr"/>
+      <c r="R359" s="2" t="inlineStr"/>
+      <c r="S359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/walperdrinks</t>
+        </is>
+      </c>
+      <c r="T359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/walper.drinks</t>
+        </is>
+      </c>
+      <c r="U359" s="2" t="inlineStr"/>
+      <c r="V359" s="2" t="inlineStr"/>
+      <c r="W359" s="2" t="inlineStr"/>
+      <c r="X359" s="2" t="inlineStr"/>
+      <c r="Y359" s="2" t="inlineStr"/>
+      <c r="Z359" s="2" t="inlineStr"/>
+      <c r="AA359" s="2" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>MARCO ITALIANO s.r.o.</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr"/>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>168461</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr"/>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>Tomašíkova 3/A</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>821 01</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marcoitaliano.sk</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr"/>
+      <c r="K360" s="2" t="inlineStr"/>
+      <c r="L360" s="2" t="inlineStr"/>
+      <c r="M360" s="2" t="inlineStr"/>
+      <c r="N360" s="2" t="inlineStr">
+        <is>
+          <t>objednavky@marcoitaliano.sk</t>
+        </is>
+      </c>
+      <c r="O360" s="2" t="inlineStr"/>
+      <c r="P360" s="2" t="inlineStr"/>
+      <c r="Q360" s="2" t="inlineStr"/>
+      <c r="R360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/marco-italiano/</t>
+        </is>
+      </c>
+      <c r="S360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/alimentarimarco</t>
+        </is>
+      </c>
+      <c r="T360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/marcoitalianospeciality/</t>
+        </is>
+      </c>
+      <c r="U360" s="2" t="inlineStr"/>
+      <c r="V360" s="2" t="inlineStr"/>
+      <c r="W360" s="2" t="inlineStr"/>
+      <c r="X360" s="2" t="inlineStr"/>
+      <c r="Y360" s="2" t="inlineStr"/>
+      <c r="Z360" s="2" t="inlineStr"/>
+      <c r="AA360" s="2" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>Unique Distribution SK s.r.o.</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr"/>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>168460</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>Komárno</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr"/>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>Hadovce 278</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>945 01</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>https://uspirits.sk</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr"/>
+      <c r="K361" s="2" t="inlineStr"/>
+      <c r="L361" s="2" t="inlineStr"/>
+      <c r="M361" s="2" t="inlineStr"/>
+      <c r="N361" s="2" t="inlineStr">
+        <is>
+          <t>hello@uspirits.sk</t>
+        </is>
+      </c>
+      <c r="O361" s="2" t="inlineStr"/>
+      <c r="P361" s="2" t="inlineStr"/>
+      <c r="Q361" s="2" t="inlineStr"/>
+      <c r="R361" s="2" t="inlineStr"/>
+      <c r="S361" s="2" t="inlineStr"/>
+      <c r="T361" s="2" t="inlineStr"/>
+      <c r="U361" s="2" t="inlineStr"/>
+      <c r="V361" s="2" t="inlineStr"/>
+      <c r="W361" s="2" t="inlineStr"/>
+      <c r="X361" s="2" t="inlineStr"/>
+      <c r="Y361" s="2" t="inlineStr"/>
+      <c r="Z361" s="2" t="inlineStr"/>
+      <c r="AA361" s="2" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>Best Coffee &amp; Spirits, s. r. o.</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr"/>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>168459</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>Laurinská 210/8</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>811 01</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>https://bestcoffee.sk</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr"/>
+      <c r="K362" s="2" t="inlineStr"/>
+      <c r="L362" s="2" t="inlineStr"/>
+      <c r="M362" s="2" t="inlineStr"/>
+      <c r="N362" s="2" t="inlineStr">
+        <is>
+          <t>info@bestcoffee.sk</t>
+        </is>
+      </c>
+      <c r="O362" s="2" t="inlineStr"/>
+      <c r="P362" s="2" t="inlineStr"/>
+      <c r="Q362" s="2" t="inlineStr"/>
+      <c r="R362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/best-coffee-spirits/</t>
+        </is>
+      </c>
+      <c r="S362" s="2" t="inlineStr"/>
+      <c r="T362" s="2" t="inlineStr"/>
+      <c r="U362" s="2" t="inlineStr"/>
+      <c r="V362" s="2" t="inlineStr"/>
+      <c r="W362" s="2" t="inlineStr">
+        <is>
+          <t>Marco Destefanis</t>
+        </is>
+      </c>
+      <c r="X362" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y362" s="2" t="inlineStr"/>
+      <c r="Z362" s="2" t="inlineStr"/>
+      <c r="AA362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marco-destefanis-40a53627/</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>Best Coffee &amp; Spirits, s. r. o.</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr"/>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>168459</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>Laurinská 210/8</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>811 01</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>https://bestcoffee.sk</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr"/>
+      <c r="K363" s="2" t="inlineStr"/>
+      <c r="L363" s="2" t="inlineStr"/>
+      <c r="M363" s="2" t="inlineStr"/>
+      <c r="N363" s="2" t="inlineStr">
+        <is>
+          <t>info@bestcoffee.sk</t>
+        </is>
+      </c>
+      <c r="O363" s="2" t="inlineStr"/>
+      <c r="P363" s="2" t="inlineStr"/>
+      <c r="Q363" s="2" t="inlineStr"/>
+      <c r="R363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/best-coffee-spirits/</t>
+        </is>
+      </c>
+      <c r="S363" s="2" t="inlineStr"/>
+      <c r="T363" s="2" t="inlineStr"/>
+      <c r="U363" s="2" t="inlineStr"/>
+      <c r="V363" s="2" t="inlineStr"/>
+      <c r="W363" s="2" t="inlineStr">
+        <is>
+          <t>Ján Konečný</t>
+        </is>
+      </c>
+      <c r="X363" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="Y363" s="2" t="inlineStr"/>
+      <c r="Z363" s="2" t="inlineStr"/>
+      <c r="AA363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/j%C3%A1n-kone%C4%8Dn%C3%BD-6879b7151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>Happy Bottle s.r.o.</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr"/>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>168457</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>Košice</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>Košice Region</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>Hlavná 38/70</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>040 01</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.happybottle.sk</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr"/>
+      <c r="K364" s="2" t="inlineStr"/>
+      <c r="L364" s="2" t="inlineStr"/>
+      <c r="M364" s="2" t="inlineStr"/>
+      <c r="N364" s="2" t="inlineStr">
+        <is>
+          <t>obchod@happybottle.sk</t>
+        </is>
+      </c>
+      <c r="O364" s="2" t="inlineStr"/>
+      <c r="P364" s="2" t="inlineStr"/>
+      <c r="Q364" s="2" t="inlineStr"/>
+      <c r="R364" s="2" t="inlineStr"/>
+      <c r="S364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Happy-Bottle-100082990927954/</t>
+        </is>
+      </c>
+      <c r="T364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/happybottle.sk/</t>
+        </is>
+      </c>
+      <c r="U364" s="2" t="inlineStr"/>
+      <c r="V364" s="2" t="inlineStr"/>
+      <c r="W364" s="2" t="inlineStr"/>
+      <c r="X364" s="2" t="inlineStr"/>
+      <c r="Y364" s="2" t="inlineStr"/>
+      <c r="Z364" s="2" t="inlineStr"/>
+      <c r="AA364" s="2" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>Moravinum s.r.o.</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr"/>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>168456</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>Cabanová 13/D</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>841 02</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moravinum.sk</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr"/>
+      <c r="K365" s="2" t="inlineStr"/>
+      <c r="L365" s="2" t="inlineStr"/>
+      <c r="M365" s="2" t="inlineStr"/>
+      <c r="N365" s="2" t="inlineStr">
+        <is>
+          <t>info@moravinum.sk</t>
+        </is>
+      </c>
+      <c r="O365" s="2" t="inlineStr"/>
+      <c r="P365" s="2" t="inlineStr"/>
+      <c r="Q365" s="2" t="inlineStr"/>
+      <c r="R365" s="2" t="inlineStr"/>
+      <c r="S365" s="2" t="inlineStr"/>
+      <c r="T365" s="2" t="inlineStr"/>
+      <c r="U365" s="2" t="inlineStr"/>
+      <c r="V365" s="2" t="inlineStr"/>
+      <c r="W365" s="2" t="inlineStr">
+        <is>
+          <t>Tomáš Foltin</t>
+        </is>
+      </c>
+      <c r="X365" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="Y365" s="2" t="inlineStr"/>
+      <c r="Z365" s="2" t="inlineStr"/>
+      <c r="AA365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomas-foltin-lean-6-sigma/</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>INWINE s.r.o.</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr"/>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>168455</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>Jána Langoša 1</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>841 03</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>https://inwine.sk</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr"/>
+      <c r="K366" s="2" t="inlineStr"/>
+      <c r="L366" s="2" t="inlineStr"/>
+      <c r="M366" s="2" t="inlineStr"/>
+      <c r="N366" s="2" t="inlineStr">
+        <is>
+          <t>skoda@inwine.sk</t>
+        </is>
+      </c>
+      <c r="O366" s="2" t="inlineStr"/>
+      <c r="P366" s="2" t="inlineStr"/>
+      <c r="Q366" s="2" t="inlineStr"/>
+      <c r="R366" s="2" t="inlineStr"/>
+      <c r="S366" s="2" t="inlineStr"/>
+      <c r="T366" s="2" t="inlineStr"/>
+      <c r="U366" s="2" t="inlineStr"/>
+      <c r="V366" s="2" t="inlineStr"/>
+      <c r="W366" s="2" t="inlineStr">
+        <is>
+          <t>Milan Brodziansky</t>
+        </is>
+      </c>
+      <c r="X366" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="Y366" s="2" t="inlineStr"/>
+      <c r="Z366" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA366" s="2" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>INWINE s.r.o.</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr"/>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>168455</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>Jána Langoša 1</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>841 03</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>https://inwine.sk</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr"/>
+      <c r="K367" s="2" t="inlineStr"/>
+      <c r="L367" s="2" t="inlineStr"/>
+      <c r="M367" s="2" t="inlineStr"/>
+      <c r="N367" s="2" t="inlineStr">
+        <is>
+          <t>skoda@inwine.sk</t>
+        </is>
+      </c>
+      <c r="O367" s="2" t="inlineStr"/>
+      <c r="P367" s="2" t="inlineStr"/>
+      <c r="Q367" s="2" t="inlineStr"/>
+      <c r="R367" s="2" t="inlineStr"/>
+      <c r="S367" s="2" t="inlineStr"/>
+      <c r="T367" s="2" t="inlineStr"/>
+      <c r="U367" s="2" t="inlineStr"/>
+      <c r="V367" s="2" t="inlineStr"/>
+      <c r="W367" s="2" t="inlineStr">
+        <is>
+          <t>Ing. Roman Gápel</t>
+        </is>
+      </c>
+      <c r="X367" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y367" s="2" t="inlineStr"/>
+      <c r="Z367" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA367" s="2" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>INWINE s.r.o.</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr"/>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>168455</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>Jána Langoša 1</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>841 03</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>https://inwine.sk</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr"/>
+      <c r="K368" s="2" t="inlineStr"/>
+      <c r="L368" s="2" t="inlineStr"/>
+      <c r="M368" s="2" t="inlineStr"/>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>skoda@inwine.sk</t>
+        </is>
+      </c>
+      <c r="O368" s="2" t="inlineStr"/>
+      <c r="P368" s="2" t="inlineStr"/>
+      <c r="Q368" s="2" t="inlineStr"/>
+      <c r="R368" s="2" t="inlineStr"/>
+      <c r="S368" s="2" t="inlineStr"/>
+      <c r="T368" s="2" t="inlineStr"/>
+      <c r="U368" s="2" t="inlineStr"/>
+      <c r="V368" s="2" t="inlineStr"/>
+      <c r="W368" s="2" t="inlineStr">
+        <is>
+          <t>Peter Skoda</t>
+        </is>
+      </c>
+      <c r="X368" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="Y368" s="2" t="inlineStr"/>
+      <c r="Z368" s="2" t="inlineStr"/>
+      <c r="AA368" s="2" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>Superlativo s.r.o.</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr"/>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>168454</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava - Staré Mesto</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>Galandova 1155/5</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>811 06</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>https://superlativo.sk</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr"/>
+      <c r="K369" s="2" t="inlineStr"/>
+      <c r="L369" s="2" t="inlineStr"/>
+      <c r="M369" s="2" t="inlineStr"/>
+      <c r="N369" s="2" t="inlineStr">
+        <is>
+          <t>Info@Superlativo.sk</t>
+        </is>
+      </c>
+      <c r="O369" s="2" t="inlineStr"/>
+      <c r="P369" s="2" t="inlineStr"/>
+      <c r="Q369" s="2" t="inlineStr"/>
+      <c r="R369" s="2" t="inlineStr"/>
+      <c r="S369" s="2" t="inlineStr"/>
+      <c r="T369" s="2" t="inlineStr"/>
+      <c r="U369" s="2" t="inlineStr"/>
+      <c r="V369" s="2" t="inlineStr"/>
+      <c r="W369" s="2" t="inlineStr">
+        <is>
+          <t>Sauro Lonardi</t>
+        </is>
+      </c>
+      <c r="X369" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y369" s="2" t="inlineStr"/>
+      <c r="Z369" s="2" t="inlineStr"/>
+      <c r="AA369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/saurolonardi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>Sip and Smith s. r. o.</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr"/>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>168453</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>Nezábudková 5</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>821 01</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sipandsmith.sk</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr"/>
+      <c r="K370" s="2" t="inlineStr"/>
+      <c r="L370" s="2" t="inlineStr"/>
+      <c r="M370" s="2" t="inlineStr"/>
+      <c r="N370" s="2" t="inlineStr">
+        <is>
+          <t>regina@sipandsmith.sk</t>
+        </is>
+      </c>
+      <c r="O370" s="2" t="inlineStr"/>
+      <c r="P370" s="2" t="inlineStr"/>
+      <c r="Q370" s="2" t="inlineStr"/>
+      <c r="R370" s="2" t="inlineStr"/>
+      <c r="S370" s="2" t="inlineStr"/>
+      <c r="T370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sipandsmith</t>
+        </is>
+      </c>
+      <c r="U370" s="2" t="inlineStr"/>
+      <c r="V370" s="2" t="inlineStr"/>
+      <c r="W370" s="2" t="inlineStr"/>
+      <c r="X370" s="2" t="inlineStr"/>
+      <c r="Y370" s="2" t="inlineStr"/>
+      <c r="Z370" s="2" t="inlineStr"/>
+      <c r="AA370" s="2" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>PRIMAVINO - Matej Lanko</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr"/>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>168451</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>Hradište pod Vrátnom</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>Slovensko</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>Hradište pod Vrátnom, 348</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>906 12</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>https://primavino.sk</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr"/>
+      <c r="K371" s="2" t="inlineStr"/>
+      <c r="L371" s="2" t="inlineStr"/>
+      <c r="M371" s="2" t="inlineStr"/>
+      <c r="N371" s="2" t="inlineStr">
+        <is>
+          <t>info@primavino.sk</t>
+        </is>
+      </c>
+      <c r="O371" s="2" t="inlineStr"/>
+      <c r="P371" s="2" t="inlineStr"/>
+      <c r="Q371" s="2" t="inlineStr"/>
+      <c r="R371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/primavino-slovakia/</t>
+        </is>
+      </c>
+      <c r="S371" s="2" t="inlineStr"/>
+      <c r="T371" s="2" t="inlineStr"/>
+      <c r="U371" s="2" t="inlineStr"/>
+      <c r="V371" s="2" t="inlineStr"/>
+      <c r="W371" s="2" t="inlineStr">
+        <is>
+          <t>Matej Lanko</t>
+        </is>
+      </c>
+      <c r="X371" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y371" s="2" t="inlineStr"/>
+      <c r="Z371" s="2" t="inlineStr"/>
+      <c r="AA371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lankomatej/</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>MEGAN s.r.o.</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr"/>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>168450</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr"/>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>Agátová 7A</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>84101</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>https://megansro.webnode.sk</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr"/>
+      <c r="K372" s="2" t="inlineStr"/>
+      <c r="L372" s="2" t="inlineStr"/>
+      <c r="M372" s="2" t="inlineStr"/>
+      <c r="N372" s="2" t="inlineStr">
+        <is>
+          <t>salesmegansk@gmail.com</t>
+        </is>
+      </c>
+      <c r="O372" s="2" t="inlineStr"/>
+      <c r="P372" s="2" t="inlineStr"/>
+      <c r="Q372" s="2" t="inlineStr"/>
+      <c r="R372" s="2" t="inlineStr"/>
+      <c r="S372" s="2" t="inlineStr"/>
+      <c r="T372" s="2" t="inlineStr"/>
+      <c r="U372" s="2" t="inlineStr"/>
+      <c r="V372" s="2" t="inlineStr"/>
+      <c r="W372" s="2" t="inlineStr"/>
+      <c r="X372" s="2" t="inlineStr"/>
+      <c r="Y372" s="2" t="inlineStr"/>
+      <c r="Z372" s="2" t="inlineStr"/>
+      <c r="AA372" s="2" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>BACARI GROUP / Xepap &amp; Boccor s.r.o.</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr"/>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>168449</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr"/>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>Jarabinkova 6B</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>8210 09</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>https://bacari.sk, https://boccordelights.sk</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr"/>
+      <c r="K373" s="2" t="inlineStr"/>
+      <c r="L373" s="2" t="inlineStr"/>
+      <c r="M373" s="2" t="inlineStr"/>
+      <c r="N373" s="2" t="inlineStr">
+        <is>
+          <t>contact@bacari.sk</t>
+        </is>
+      </c>
+      <c r="O373" s="2" t="inlineStr"/>
+      <c r="P373" s="2" t="inlineStr"/>
+      <c r="Q373" s="2" t="inlineStr"/>
+      <c r="R373" s="2" t="inlineStr"/>
+      <c r="S373" s="2" t="inlineStr"/>
+      <c r="T373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boccordelights.sk/</t>
+        </is>
+      </c>
+      <c r="U373" s="2" t="inlineStr"/>
+      <c r="V373" s="2" t="inlineStr"/>
+      <c r="W373" s="2" t="inlineStr"/>
+      <c r="X373" s="2" t="inlineStr"/>
+      <c r="Y373" s="2" t="inlineStr"/>
+      <c r="Z373" s="2" t="inlineStr"/>
+      <c r="AA373" s="2" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>ZOTEKS s. r. o.</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr"/>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>168448</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr"/>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>Košická 49</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>821 08</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.impresario.sk</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr"/>
+      <c r="K374" s="2" t="inlineStr"/>
+      <c r="L374" s="2" t="inlineStr"/>
+      <c r="M374" s="2" t="inlineStr"/>
+      <c r="N374" s="2" t="inlineStr">
+        <is>
+          <t>support@smartweb.sk</t>
+        </is>
+      </c>
+      <c r="O374" s="2" t="inlineStr"/>
+      <c r="P374" s="2" t="inlineStr"/>
+      <c r="Q374" s="2" t="inlineStr"/>
+      <c r="R374" s="2" t="inlineStr"/>
+      <c r="S374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/impresario.sk/</t>
+        </is>
+      </c>
+      <c r="T374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/impresario.sk/</t>
+        </is>
+      </c>
+      <c r="U374" s="2" t="inlineStr"/>
+      <c r="V374" s="2" t="inlineStr"/>
+      <c r="W374" s="2" t="inlineStr"/>
+      <c r="X374" s="2" t="inlineStr"/>
+      <c r="Y374" s="2" t="inlineStr"/>
+      <c r="Z374" s="2" t="inlineStr"/>
+      <c r="AA374" s="2" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>Rudolf Ruža</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr"/>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>168447</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>Malacky</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr"/>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>Štefana Čulena 6</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>901 01</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ruzavo.sk</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr"/>
+      <c r="K375" s="2" t="inlineStr"/>
+      <c r="L375" s="2" t="inlineStr"/>
+      <c r="M375" s="2" t="inlineStr"/>
+      <c r="N375" s="2" t="inlineStr">
+        <is>
+          <t>eshop@ruzavo.sk</t>
+        </is>
+      </c>
+      <c r="O375" s="2" t="inlineStr"/>
+      <c r="P375" s="2" t="inlineStr"/>
+      <c r="Q375" s="2" t="inlineStr"/>
+      <c r="R375" s="2" t="inlineStr"/>
+      <c r="S375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ruzaalkonealko</t>
+        </is>
+      </c>
+      <c r="T375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruza_alko_nealko/</t>
+        </is>
+      </c>
+      <c r="U375" s="2" t="inlineStr"/>
+      <c r="V375" s="2" t="inlineStr"/>
+      <c r="W375" s="2" t="inlineStr"/>
+      <c r="X375" s="2" t="inlineStr"/>
+      <c r="Y375" s="2" t="inlineStr"/>
+      <c r="Z375" s="2" t="inlineStr"/>
+      <c r="AA375" s="2" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>Winepalenik / Robert Páleník</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr"/>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>168446</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr"/>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>Ševčenkova 1</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>851 01</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winepalenik.com</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr"/>
+      <c r="K376" s="2" t="inlineStr"/>
+      <c r="L376" s="2" t="inlineStr"/>
+      <c r="M376" s="2" t="inlineStr"/>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>info@winepalenik.com</t>
+        </is>
+      </c>
+      <c r="O376" s="2" t="inlineStr"/>
+      <c r="P376" s="2" t="inlineStr"/>
+      <c r="Q376" s="2" t="inlineStr"/>
+      <c r="R376" s="2" t="inlineStr"/>
+      <c r="S376" s="2" t="inlineStr"/>
+      <c r="T376" s="2" t="inlineStr"/>
+      <c r="U376" s="2" t="inlineStr"/>
+      <c r="V376" s="2" t="inlineStr"/>
+      <c r="W376" s="2" t="inlineStr"/>
+      <c r="X376" s="2" t="inlineStr"/>
+      <c r="Y376" s="2" t="inlineStr"/>
+      <c r="Z376" s="2" t="inlineStr"/>
+      <c r="AA376" s="2" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>DFD Trading, spol. s r. o.</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr"/>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>168445</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>Gorkého 3</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>811 01</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>https://dfdtrading.sk</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr"/>
+      <c r="K377" s="2" t="inlineStr"/>
+      <c r="L377" s="2" t="inlineStr"/>
+      <c r="M377" s="2" t="inlineStr"/>
+      <c r="N377" s="2" t="inlineStr">
+        <is>
+          <t>info@dfdtrading.sk</t>
+        </is>
+      </c>
+      <c r="O377" s="2" t="inlineStr"/>
+      <c r="P377" s="2" t="inlineStr"/>
+      <c r="Q377" s="2" t="inlineStr"/>
+      <c r="R377" s="2" t="inlineStr"/>
+      <c r="S377" s="2" t="inlineStr"/>
+      <c r="T377" s="2" t="inlineStr"/>
+      <c r="U377" s="2" t="inlineStr"/>
+      <c r="V377" s="2" t="inlineStr"/>
+      <c r="W377" s="2" t="inlineStr">
+        <is>
+          <t>Tomas Stolarik</t>
+        </is>
+      </c>
+      <c r="X377" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y377" s="2" t="inlineStr"/>
+      <c r="Z377" s="2" t="inlineStr"/>
+      <c r="AA377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomas-stolarik-a4091788/</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>MEGAS trade, s.r.o.</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr"/>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>168444</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>Kežmarok</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr"/>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>Michalská 18</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>060 01</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.megas.sk</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr"/>
+      <c r="K378" s="2" t="inlineStr"/>
+      <c r="L378" s="2" t="inlineStr"/>
+      <c r="M378" s="2" t="inlineStr"/>
+      <c r="N378" s="2" t="inlineStr">
+        <is>
+          <t>info@allinmarket.sk</t>
+        </is>
+      </c>
+      <c r="O378" s="2" t="inlineStr">
+        <is>
+          <t>+421 52 468 51 95</t>
+        </is>
+      </c>
+      <c r="P378" s="2" t="inlineStr"/>
+      <c r="Q378" s="2" t="inlineStr"/>
+      <c r="R378" s="2" t="inlineStr"/>
+      <c r="S378" s="2" t="inlineStr"/>
+      <c r="T378" s="2" t="inlineStr"/>
+      <c r="U378" s="2" t="inlineStr"/>
+      <c r="V378" s="2" t="inlineStr"/>
+      <c r="W378" s="2" t="inlineStr"/>
+      <c r="X378" s="2" t="inlineStr"/>
+      <c r="Y378" s="2" t="inlineStr"/>
+      <c r="Z378" s="2" t="inlineStr"/>
+      <c r="AA378" s="2" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>Domenico Cigar, s. r. o.</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr"/>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>168443</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>Gogoľova 18</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>851 01</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.domenicocigar.com</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr"/>
+      <c r="K379" s="2" t="inlineStr"/>
+      <c r="L379" s="2" t="inlineStr"/>
+      <c r="M379" s="2" t="inlineStr"/>
+      <c r="N379" s="2" t="inlineStr">
+        <is>
+          <t>info@domenicocigar.com</t>
+        </is>
+      </c>
+      <c r="O379" s="2" t="inlineStr"/>
+      <c r="P379" s="2" t="inlineStr"/>
+      <c r="Q379" s="2" t="inlineStr"/>
+      <c r="R379" s="2" t="inlineStr"/>
+      <c r="S379" s="2" t="inlineStr"/>
+      <c r="T379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/domenicocigar/</t>
+        </is>
+      </c>
+      <c r="U379" s="2" t="inlineStr"/>
+      <c r="V379" s="2" t="inlineStr"/>
+      <c r="W379" s="2" t="inlineStr">
+        <is>
+          <t>Tomas Sokol</t>
+        </is>
+      </c>
+      <c r="X379" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y379" s="2" t="inlineStr"/>
+      <c r="Z379" s="2" t="inlineStr"/>
+      <c r="AA379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tomas-sokol-5a550b4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>Gulová Jana</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr"/>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>168442</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>Dubnica nad Vahom</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr"/>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>Pod Hajom 4058/209</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>01841</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>http://www.talianskedelikatesy.sk</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr"/>
+      <c r="K380" s="2" t="inlineStr"/>
+      <c r="L380" s="2" t="inlineStr"/>
+      <c r="M380" s="2" t="inlineStr"/>
+      <c r="N380" s="2" t="inlineStr">
+        <is>
+          <t>gulova@talianskedelikatesy.sk</t>
+        </is>
+      </c>
+      <c r="O380" s="2" t="inlineStr"/>
+      <c r="P380" s="2" t="inlineStr"/>
+      <c r="Q380" s="2" t="inlineStr"/>
+      <c r="R380" s="2" t="inlineStr"/>
+      <c r="S380" s="2" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/pages/Talianske-delikatesy/264071683606474</t>
+        </is>
+      </c>
+      <c r="T380" s="2" t="inlineStr"/>
+      <c r="U380" s="2" t="inlineStr"/>
+      <c r="V380" s="2" t="inlineStr"/>
+      <c r="W380" s="2" t="inlineStr"/>
+      <c r="X380" s="2" t="inlineStr"/>
+      <c r="Y380" s="2" t="inlineStr"/>
+      <c r="Z380" s="2" t="inlineStr"/>
+      <c r="AA380" s="2" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>KERUCOK s.r.o.</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr"/>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>168441</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>Sabinov</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr"/>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>Mieru 20</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>083 01</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>http://www.kerucok.sk</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr"/>
+      <c r="K381" s="2" t="inlineStr"/>
+      <c r="L381" s="2" t="inlineStr"/>
+      <c r="M381" s="2" t="inlineStr"/>
+      <c r="N381" s="2" t="inlineStr">
+        <is>
+          <t>distribucia@kerucok.sk</t>
+        </is>
+      </c>
+      <c r="O381" s="2" t="inlineStr"/>
+      <c r="P381" s="2" t="inlineStr"/>
+      <c r="Q381" s="2" t="inlineStr"/>
+      <c r="R381" s="2" t="inlineStr"/>
+      <c r="S381" s="2" t="inlineStr"/>
+      <c r="T381" s="2" t="inlineStr"/>
+      <c r="U381" s="2" t="inlineStr"/>
+      <c r="V381" s="2" t="inlineStr"/>
+      <c r="W381" s="2" t="inlineStr"/>
+      <c r="X381" s="2" t="inlineStr"/>
+      <c r="Y381" s="2" t="inlineStr"/>
+      <c r="Z381" s="2" t="inlineStr"/>
+      <c r="AA381" s="2" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>Alkoholonline.sk</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr"/>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>168440</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>Prešov</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr"/>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>Okružná 3030/29</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>080 01</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alkoholonline.sk</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr"/>
+      <c r="K382" s="2" t="inlineStr"/>
+      <c r="L382" s="2" t="inlineStr"/>
+      <c r="M382" s="2" t="inlineStr"/>
+      <c r="N382" s="2" t="inlineStr">
+        <is>
+          <t>ahoj@alkoholonline.sk</t>
+        </is>
+      </c>
+      <c r="O382" s="2" t="inlineStr"/>
+      <c r="P382" s="2" t="inlineStr"/>
+      <c r="Q382" s="2" t="inlineStr"/>
+      <c r="R382" s="2" t="inlineStr"/>
+      <c r="S382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/alkoholonlinesk</t>
+        </is>
+      </c>
+      <c r="T382" s="2" t="inlineStr"/>
+      <c r="U382" s="2" t="inlineStr"/>
+      <c r="V382" s="2" t="inlineStr"/>
+      <c r="W382" s="2" t="inlineStr"/>
+      <c r="X382" s="2" t="inlineStr"/>
+      <c r="Y382" s="2" t="inlineStr"/>
+      <c r="Z382" s="2" t="inlineStr"/>
+      <c r="AA382" s="2" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>ESPANIAN / spanielskevina.sk</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr"/>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>168439</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>Plzenská 9</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>831 03</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>https://spanielskevina.sk, https://www.espanian.sk</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr"/>
+      <c r="K383" s="2" t="inlineStr"/>
+      <c r="L383" s="2" t="inlineStr"/>
+      <c r="M383" s="2" t="inlineStr"/>
+      <c r="N383" s="2" t="inlineStr">
+        <is>
+          <t>info@espanian.sk</t>
+        </is>
+      </c>
+      <c r="O383" s="2" t="inlineStr"/>
+      <c r="P383" s="2" t="inlineStr"/>
+      <c r="Q383" s="2" t="inlineStr"/>
+      <c r="R383" s="2" t="inlineStr"/>
+      <c r="S383" s="2" t="inlineStr"/>
+      <c r="T383" s="2" t="inlineStr"/>
+      <c r="U383" s="2" t="inlineStr"/>
+      <c r="V383" s="2" t="inlineStr"/>
+      <c r="W383" s="2" t="inlineStr"/>
+      <c r="X383" s="2" t="inlineStr"/>
+      <c r="Y383" s="2" t="inlineStr"/>
+      <c r="Z383" s="2" t="inlineStr"/>
+      <c r="AA383" s="2" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>Neverland s.r.o.</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr"/>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>168438</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>Rakytovská cesta 2630/1C</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.neverland.sk</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr"/>
+      <c r="K384" s="2" t="inlineStr"/>
+      <c r="L384" s="2" t="inlineStr"/>
+      <c r="M384" s="2" t="inlineStr"/>
+      <c r="N384" s="2" t="inlineStr">
+        <is>
+          <t>trade@neverland.sk</t>
+        </is>
+      </c>
+      <c r="O384" s="2" t="inlineStr"/>
+      <c r="P384" s="2" t="inlineStr"/>
+      <c r="Q384" s="2" t="inlineStr"/>
+      <c r="R384" s="2" t="inlineStr"/>
+      <c r="S384" s="2" t="inlineStr"/>
+      <c r="T384" s="2" t="inlineStr"/>
+      <c r="U384" s="2" t="inlineStr"/>
+      <c r="V384" s="2" t="inlineStr"/>
+      <c r="W384" s="2" t="inlineStr"/>
+      <c r="X384" s="2" t="inlineStr"/>
+      <c r="Y384" s="2" t="inlineStr"/>
+      <c r="Z384" s="2" t="inlineStr"/>
+      <c r="AA384" s="2" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>Fine-Wines Distribution s.r.o.</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr"/>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>168437</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr"/>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>Dunajska 2514/34</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr"/>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fine-wines.sk</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr"/>
+      <c r="K385" s="2" t="inlineStr"/>
+      <c r="L385" s="2" t="inlineStr"/>
+      <c r="M385" s="2" t="inlineStr"/>
+      <c r="N385" s="2" t="inlineStr">
+        <is>
+          <t>office@fine-wines.sk</t>
+        </is>
+      </c>
+      <c r="O385" s="2" t="inlineStr"/>
+      <c r="P385" s="2" t="inlineStr"/>
+      <c r="Q385" s="2" t="inlineStr"/>
+      <c r="R385" s="2" t="inlineStr"/>
+      <c r="S385" s="2" t="inlineStr"/>
+      <c r="T385" s="2" t="inlineStr"/>
+      <c r="U385" s="2" t="inlineStr"/>
+      <c r="V385" s="2" t="inlineStr"/>
+      <c r="W385" s="2" t="inlineStr"/>
+      <c r="X385" s="2" t="inlineStr"/>
+      <c r="Y385" s="2" t="inlineStr"/>
+      <c r="Z385" s="2" t="inlineStr"/>
+      <c r="AA385" s="2" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>Corner Sk Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>Corner Sk Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>103152</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>3060/39 Stará Vajnorská</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cornerco.sk, https://wineplanet.sk, https://www.corner.sk</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr"/>
+      <c r="K386" s="2" t="inlineStr"/>
+      <c r="L386" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M386" s="2" t="inlineStr"/>
+      <c r="N386" s="2" t="inlineStr">
+        <is>
+          <t>corner@corner.sk</t>
+        </is>
+      </c>
+      <c r="O386" s="2" t="inlineStr">
+        <is>
+          <t>+421 2455 276 61</t>
+        </is>
+      </c>
+      <c r="P386" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q386" s="2" t="inlineStr">
+        <is>
+          <t>31377971</t>
+        </is>
+      </c>
+      <c r="R386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/corner-sk-ltd-spol-s-r-o-/</t>
+        </is>
+      </c>
+      <c r="S386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineplanet/</t>
+        </is>
+      </c>
+      <c r="T386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineplanetsk/</t>
+        </is>
+      </c>
+      <c r="U386" s="2" t="inlineStr"/>
+      <c r="V386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/WineplanetVino/</t>
+        </is>
+      </c>
+      <c r="W386" s="2" t="inlineStr">
+        <is>
+          <t>Paulína Letková</t>
+        </is>
+      </c>
+      <c r="X386" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Head of Purchasing Department</t>
+        </is>
+      </c>
+      <c r="Y386" s="2" t="inlineStr"/>
+      <c r="Z386" s="2" t="inlineStr"/>
+      <c r="AA386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paul%C3%ADna-letkov%C3%A1-46a75b2a7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>Corner Sk Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>Corner Sk Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>103152</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>3060/39 Stará Vajnorská</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cornerco.sk, https://wineplanet.sk, https://www.corner.sk</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr"/>
+      <c r="K387" s="2" t="inlineStr"/>
+      <c r="L387" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M387" s="2" t="inlineStr"/>
+      <c r="N387" s="2" t="inlineStr">
+        <is>
+          <t>corner@corner.sk</t>
+        </is>
+      </c>
+      <c r="O387" s="2" t="inlineStr">
+        <is>
+          <t>+421 2455 276 61</t>
+        </is>
+      </c>
+      <c r="P387" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q387" s="2" t="inlineStr">
+        <is>
+          <t>31377971</t>
+        </is>
+      </c>
+      <c r="R387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/corner-sk-ltd-spol-s-r-o-/</t>
+        </is>
+      </c>
+      <c r="S387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineplanet/</t>
+        </is>
+      </c>
+      <c r="T387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineplanetsk/</t>
+        </is>
+      </c>
+      <c r="U387" s="2" t="inlineStr"/>
+      <c r="V387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/WineplanetVino/</t>
+        </is>
+      </c>
+      <c r="W387" s="2" t="inlineStr">
+        <is>
+          <t>Marian Kubis</t>
+        </is>
+      </c>
+      <c r="X387" s="2" t="inlineStr">
+        <is>
+          <t>Executive Sales Director</t>
+        </is>
+      </c>
+      <c r="Y387" s="2" t="inlineStr"/>
+      <c r="Z387" s="2" t="inlineStr"/>
+      <c r="AA387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kubis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>Corner Sk Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>Corner Sk Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>103152</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>3060/39 Stará Vajnorská</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cornerco.sk, https://wineplanet.sk, https://www.corner.sk</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr"/>
+      <c r="K388" s="2" t="inlineStr"/>
+      <c r="L388" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M388" s="2" t="inlineStr"/>
+      <c r="N388" s="2" t="inlineStr">
+        <is>
+          <t>corner@corner.sk</t>
+        </is>
+      </c>
+      <c r="O388" s="2" t="inlineStr">
+        <is>
+          <t>+421 2455 276 61</t>
+        </is>
+      </c>
+      <c r="P388" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q388" s="2" t="inlineStr">
+        <is>
+          <t>31377971</t>
+        </is>
+      </c>
+      <c r="R388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/corner-sk-ltd-spol-s-r-o-/</t>
+        </is>
+      </c>
+      <c r="S388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineplanet/</t>
+        </is>
+      </c>
+      <c r="T388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineplanetsk/</t>
+        </is>
+      </c>
+      <c r="U388" s="2" t="inlineStr"/>
+      <c r="V388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/WineplanetVino/</t>
+        </is>
+      </c>
+      <c r="W388" s="2" t="inlineStr">
+        <is>
+          <t>Richard Oros</t>
+        </is>
+      </c>
+      <c r="X388" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y388" s="2" t="inlineStr"/>
+      <c r="Z388" s="2" t="inlineStr"/>
+      <c r="AA388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-oros-96903965/</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>Kika Bier, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>Kika Bier, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>19466</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>Žilina</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>Brodno 81</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>010 14</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kikabier.sk</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr"/>
+      <c r="K389" s="2" t="inlineStr"/>
+      <c r="L389" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M389" s="2" t="inlineStr"/>
+      <c r="N389" s="2" t="inlineStr">
+        <is>
+          <t>kikabier@post.sk</t>
+        </is>
+      </c>
+      <c r="O389" s="2" t="inlineStr">
+        <is>
+          <t>+421 41/596 20 70</t>
+        </is>
+      </c>
+      <c r="P389" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q389" s="2" t="inlineStr">
+        <is>
+          <t>36688461</t>
+        </is>
+      </c>
+      <c r="R389" s="2" t="inlineStr"/>
+      <c r="S389" s="2" t="inlineStr"/>
+      <c r="T389" s="2" t="inlineStr"/>
+      <c r="U389" s="2" t="inlineStr"/>
+      <c r="V389" s="2" t="inlineStr"/>
+      <c r="W389" s="2" t="inlineStr"/>
+      <c r="X389" s="2" t="inlineStr"/>
+      <c r="Y389" s="2" t="inlineStr"/>
+      <c r="Z389" s="2" t="inlineStr"/>
+      <c r="AA389" s="2" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>Julk S.r.o.</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>Julk S.r.o.</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>43792</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>Vysoká pri Morave</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Malacky</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>260, 10 Družstevná</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>900 66</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.julk.sk</t>
+        </is>
+      </c>
+      <c r="J390" s="2" t="inlineStr"/>
+      <c r="K390" s="2" t="inlineStr"/>
+      <c r="L390" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="inlineStr"/>
+      <c r="N390" s="2" t="inlineStr">
+        <is>
+          <t>office@julk.sk</t>
+        </is>
+      </c>
+      <c r="O390" s="2" t="inlineStr"/>
+      <c r="P390" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q390" s="2" t="inlineStr">
+        <is>
+          <t>47436981</t>
+        </is>
+      </c>
+      <c r="R390" s="2" t="inlineStr"/>
+      <c r="S390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/julk_international_wines/100027452033991/</t>
+        </is>
+      </c>
+      <c r="T390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/julk_international_wines/</t>
+        </is>
+      </c>
+      <c r="U390" s="2" t="inlineStr"/>
+      <c r="V390" s="2" t="inlineStr"/>
+      <c r="W390" s="2" t="inlineStr">
+        <is>
+          <t>Milan Jurík</t>
+        </is>
+      </c>
+      <c r="X390" s="2" t="inlineStr">
+        <is>
+          <t>Sales/ Distribution</t>
+        </is>
+      </c>
+      <c r="Y390" s="2" t="inlineStr"/>
+      <c r="Z390" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA390" s="2" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>Julk S.r.o.</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>Julk S.r.o.</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>43792</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>Vysoká pri Morave</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Malacky</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>260, 10 Družstevná</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>900 66</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.julk.sk</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr"/>
+      <c r="K391" s="2" t="inlineStr"/>
+      <c r="L391" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M391" s="2" t="inlineStr"/>
+      <c r="N391" s="2" t="inlineStr">
+        <is>
+          <t>office@julk.sk</t>
+        </is>
+      </c>
+      <c r="O391" s="2" t="inlineStr"/>
+      <c r="P391" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t>47436981</t>
+        </is>
+      </c>
+      <c r="R391" s="2" t="inlineStr"/>
+      <c r="S391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/julk_international_wines/100027452033991/</t>
+        </is>
+      </c>
+      <c r="T391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/julk_international_wines/</t>
+        </is>
+      </c>
+      <c r="U391" s="2" t="inlineStr"/>
+      <c r="V391" s="2" t="inlineStr"/>
+      <c r="W391" s="2" t="inlineStr">
+        <is>
+          <t>Lukáš Jurík</t>
+        </is>
+      </c>
+      <c r="X391" s="2" t="inlineStr">
+        <is>
+          <t>Consultant For Companies And Gastronomy</t>
+        </is>
+      </c>
+      <c r="Y391" s="2" t="inlineStr"/>
+      <c r="Z391" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA391" s="2" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>Zlatý Vinic S.r.o.</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>Zlatý Vinic S.r.o.</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>53803</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>23 Zvolenská cesta</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>974 01</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zlatyvinic.eu</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr"/>
+      <c r="K392" s="2" t="inlineStr"/>
+      <c r="L392" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M392" s="2" t="inlineStr"/>
+      <c r="N392" s="2" t="inlineStr">
+        <is>
+          <t>eshop@zlatyvinic.eu</t>
+        </is>
+      </c>
+      <c r="O392" s="2" t="inlineStr"/>
+      <c r="P392" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q392" s="2" t="inlineStr">
+        <is>
+          <t>36838021</t>
+        </is>
+      </c>
+      <c r="R392" s="2" t="inlineStr"/>
+      <c r="S392" s="2" t="inlineStr"/>
+      <c r="T392" s="2" t="inlineStr"/>
+      <c r="U392" s="2" t="inlineStr"/>
+      <c r="V392" s="2" t="inlineStr"/>
+      <c r="W392" s="2" t="inlineStr"/>
+      <c r="X392" s="2" t="inlineStr"/>
+      <c r="Y392" s="2" t="inlineStr"/>
+      <c r="Z392" s="2" t="inlineStr"/>
+      <c r="AA392" s="2" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>146391</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>2321, 71 Piešťanská</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.sk</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr"/>
+      <c r="K393" s="2" t="inlineStr"/>
+      <c r="L393" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="M393" s="2" t="inlineStr"/>
+      <c r="N393" s="2" t="inlineStr">
+        <is>
+          <t>info@bidfood.sk</t>
+        </is>
+      </c>
+      <c r="O393" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/774 28 11</t>
+        </is>
+      </c>
+      <c r="P393" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q393" s="2" t="inlineStr">
+        <is>
+          <t>34152199</t>
+        </is>
+      </c>
+      <c r="R393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bidfood-slovakia/</t>
+        </is>
+      </c>
+      <c r="S393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfood.sk</t>
+        </is>
+      </c>
+      <c r="T393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfood_slovakia</t>
+        </is>
+      </c>
+      <c r="U393" s="2" t="inlineStr"/>
+      <c r="V393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@bidfoodslovakias.r.o.8178</t>
+        </is>
+      </c>
+      <c r="W393" s="2" t="inlineStr">
+        <is>
+          <t>Tomáš Psota</t>
+        </is>
+      </c>
+      <c r="X393" s="2" t="inlineStr">
+        <is>
+          <t>Purchase Director</t>
+        </is>
+      </c>
+      <c r="Y393" s="2" t="inlineStr"/>
+      <c r="Z393" s="2" t="inlineStr"/>
+      <c r="AA393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tom%C3%A1%C5%A1-psota-20122b295/</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>146391</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>2321, 71 Piešťanská</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.sk</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr"/>
+      <c r="K394" s="2" t="inlineStr"/>
+      <c r="L394" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="inlineStr"/>
+      <c r="N394" s="2" t="inlineStr">
+        <is>
+          <t>info@bidfood.sk</t>
+        </is>
+      </c>
+      <c r="O394" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/774 28 11</t>
+        </is>
+      </c>
+      <c r="P394" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q394" s="2" t="inlineStr">
+        <is>
+          <t>34152199</t>
+        </is>
+      </c>
+      <c r="R394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bidfood-slovakia/</t>
+        </is>
+      </c>
+      <c r="S394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfood.sk</t>
+        </is>
+      </c>
+      <c r="T394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfood_slovakia</t>
+        </is>
+      </c>
+      <c r="U394" s="2" t="inlineStr"/>
+      <c r="V394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@bidfoodslovakias.r.o.8178</t>
+        </is>
+      </c>
+      <c r="W394" s="2" t="inlineStr">
+        <is>
+          <t>Peter Slobodnik</t>
+        </is>
+      </c>
+      <c r="X394" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y394" s="2" t="inlineStr"/>
+      <c r="Z394" s="2" t="inlineStr"/>
+      <c r="AA394" s="2" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>146391</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>2321, 71 Piešťanská</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.sk</t>
+        </is>
+      </c>
+      <c r="J395" s="2" t="inlineStr"/>
+      <c r="K395" s="2" t="inlineStr"/>
+      <c r="L395" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="M395" s="2" t="inlineStr"/>
+      <c r="N395" s="2" t="inlineStr">
+        <is>
+          <t>info@bidfood.sk</t>
+        </is>
+      </c>
+      <c r="O395" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/774 28 11</t>
+        </is>
+      </c>
+      <c r="P395" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q395" s="2" t="inlineStr">
+        <is>
+          <t>34152199</t>
+        </is>
+      </c>
+      <c r="R395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bidfood-slovakia/</t>
+        </is>
+      </c>
+      <c r="S395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfood.sk</t>
+        </is>
+      </c>
+      <c r="T395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfood_slovakia</t>
+        </is>
+      </c>
+      <c r="U395" s="2" t="inlineStr"/>
+      <c r="V395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@bidfoodslovakias.r.o.8178</t>
+        </is>
+      </c>
+      <c r="W395" s="2" t="inlineStr">
+        <is>
+          <t>Peter Kadash</t>
+        </is>
+      </c>
+      <c r="X395" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y395" s="2" t="inlineStr"/>
+      <c r="Z395" s="2" t="inlineStr"/>
+      <c r="AA395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-kad%C3%A1%C5%A1-951909147/</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>Coop Jednota Cadca, Spotrebné Družstvo</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>Coop Jednota Cadca, Spotrebné Družstvo</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>146368</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>Čadca</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>87, 32 Palárikova</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>022 01</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>http://www.coopcadca.sk</t>
+        </is>
+      </c>
+      <c r="J396" s="2" t="inlineStr"/>
+      <c r="K396" s="2" t="inlineStr"/>
+      <c r="L396" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="M396" s="2" t="inlineStr"/>
+      <c r="N396" s="2" t="inlineStr">
+        <is>
+          <t>informacie@ca.coop.sk</t>
+        </is>
+      </c>
+      <c r="O396" s="2" t="inlineStr">
+        <is>
+          <t>+421 41/433 21 55</t>
+        </is>
+      </c>
+      <c r="P396" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="Q396" s="2" t="inlineStr">
+        <is>
+          <t>00168947</t>
+        </is>
+      </c>
+      <c r="R396" s="2" t="inlineStr"/>
+      <c r="S396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CJCadca</t>
+        </is>
+      </c>
+      <c r="T396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coop_jednota</t>
+        </is>
+      </c>
+      <c r="U396" s="2" t="inlineStr"/>
+      <c r="V396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@COOPJednotaSlovensko</t>
+        </is>
+      </c>
+      <c r="W396" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Janík</t>
+        </is>
+      </c>
+      <c r="X396" s="2" t="inlineStr">
+        <is>
+          <t>Chairman Of The Board Of Directors</t>
+        </is>
+      </c>
+      <c r="Y396" s="2" t="inlineStr"/>
+      <c r="Z396" s="2" t="inlineStr"/>
+      <c r="AA396" s="2" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>Coop Jednota Cadca, Spotrebné Družstvo</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>Coop Jednota Cadca, Spotrebné Družstvo</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>146368</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>Čadca</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>87, 32 Palárikova</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>022 01</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>http://www.coopcadca.sk</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr"/>
+      <c r="K397" s="2" t="inlineStr"/>
+      <c r="L397" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="M397" s="2" t="inlineStr"/>
+      <c r="N397" s="2" t="inlineStr">
+        <is>
+          <t>informacie@ca.coop.sk</t>
+        </is>
+      </c>
+      <c r="O397" s="2" t="inlineStr">
+        <is>
+          <t>+421 41/433 21 55</t>
+        </is>
+      </c>
+      <c r="P397" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="Q397" s="2" t="inlineStr">
+        <is>
+          <t>00168947</t>
+        </is>
+      </c>
+      <c r="R397" s="2" t="inlineStr"/>
+      <c r="S397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CJCadca</t>
+        </is>
+      </c>
+      <c r="T397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coop_jednota</t>
+        </is>
+      </c>
+      <c r="U397" s="2" t="inlineStr"/>
+      <c r="V397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@COOPJednotaSlovensko</t>
+        </is>
+      </c>
+      <c r="W397" s="2" t="inlineStr">
+        <is>
+          <t>Bohuslav Cyprich</t>
+        </is>
+      </c>
+      <c r="X397" s="2" t="inlineStr">
+        <is>
+          <t>Vice Chairman Of The Board Of Directors</t>
+        </is>
+      </c>
+      <c r="Y397" s="2" t="inlineStr"/>
+      <c r="Z397" s="2" t="inlineStr"/>
+      <c r="AA397" s="2" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>Infotex, Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>Infotex, Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>24829</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava II</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>8052, 78 Hradská</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>821 07</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr"/>
+      <c r="J398" s="2" t="inlineStr"/>
+      <c r="K398" s="2" t="inlineStr"/>
+      <c r="L398" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M398" s="2" t="inlineStr"/>
+      <c r="N398" s="2" t="inlineStr">
+        <is>
+          <t>info@inmedio.sk</t>
+        </is>
+      </c>
+      <c r="O398" s="2" t="inlineStr"/>
+      <c r="P398" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q398" s="2" t="inlineStr">
+        <is>
+          <t>35753692</t>
+        </is>
+      </c>
+      <c r="R398" s="2" t="inlineStr"/>
+      <c r="S398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/eshop.inmedio/</t>
+        </is>
+      </c>
+      <c r="T398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/in_medio/</t>
+        </is>
+      </c>
+      <c r="U398" s="2" t="inlineStr"/>
+      <c r="V398" s="2" t="inlineStr"/>
+      <c r="W398" s="2" t="inlineStr"/>
+      <c r="X398" s="2" t="inlineStr"/>
+      <c r="Y398" s="2" t="inlineStr"/>
+      <c r="Z398" s="2" t="inlineStr"/>
+      <c r="AA398" s="2" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>100yards &amp; Spirits, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>100yards &amp; Spirits, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>158583</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>2946, 19 Na Revíne</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>831 01</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinohlad.sk</t>
+        </is>
+      </c>
+      <c r="J399" s="2" t="inlineStr"/>
+      <c r="K399" s="2" t="inlineStr"/>
+      <c r="L399" s="2" t="inlineStr"/>
+      <c r="M399" s="2" t="inlineStr"/>
+      <c r="N399" s="2" t="inlineStr">
+        <is>
+          <t>vyriesime@vinohlad.sk</t>
+        </is>
+      </c>
+      <c r="O399" s="2" t="inlineStr"/>
+      <c r="P399" s="2" t="inlineStr"/>
+      <c r="Q399" s="2" t="inlineStr"/>
+      <c r="R399" s="2" t="inlineStr"/>
+      <c r="S399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinonastanicke/</t>
+        </is>
+      </c>
+      <c r="T399" s="2" t="inlineStr"/>
+      <c r="U399" s="2" t="inlineStr"/>
+      <c r="V399" s="2" t="inlineStr"/>
+      <c r="W399" s="2" t="inlineStr"/>
+      <c r="X399" s="2" t="inlineStr"/>
+      <c r="Y399" s="2" t="inlineStr"/>
+      <c r="Z399" s="2" t="inlineStr"/>
+      <c r="AA399" s="2" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>Eurotrade Business Services Ltd.</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>Eurotrade Business Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>82260</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>23 Royova</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>831 01</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>http://www.ebs.sk</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr"/>
+      <c r="K400" s="2" t="inlineStr"/>
+      <c r="L400" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="inlineStr"/>
+      <c r="N400" s="2" t="inlineStr">
+        <is>
+          <t>eurotrade@ebs.sk</t>
+        </is>
+      </c>
+      <c r="O400" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/654 571 29</t>
+        </is>
+      </c>
+      <c r="P400" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q400" s="2" t="inlineStr">
+        <is>
+          <t>35866845</t>
+        </is>
+      </c>
+      <c r="R400" s="2" t="inlineStr"/>
+      <c r="S400" s="2" t="inlineStr"/>
+      <c r="T400" s="2" t="inlineStr"/>
+      <c r="U400" s="2" t="inlineStr"/>
+      <c r="V400" s="2" t="inlineStr"/>
+      <c r="W400" s="2" t="inlineStr">
+        <is>
+          <t>Juraj Hanus</t>
+        </is>
+      </c>
+      <c r="X400" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y400" s="2" t="inlineStr"/>
+      <c r="Z400" s="2" t="inlineStr"/>
+      <c r="AA400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/juraj-hanus-92716b90/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Slovakia.xlsx
+++ b/BWI/bestwine_output/bestwine_Slovakia.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA400"/>
+  <dimension ref="A1:AA415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -40829,6 +40829,1513 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>Corner Sk Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>Corner Sk Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>103152</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>3060/39 Stará Vajnorská</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cornerco.sk, https://wineplanet.sk, https://www.corner.sk</t>
+        </is>
+      </c>
+      <c r="J401" s="2" t="inlineStr"/>
+      <c r="K401" s="2" t="inlineStr"/>
+      <c r="L401" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M401" s="2" t="inlineStr"/>
+      <c r="N401" s="2" t="inlineStr">
+        <is>
+          <t>corner@corner.sk</t>
+        </is>
+      </c>
+      <c r="O401" s="2" t="inlineStr">
+        <is>
+          <t>+421 2455 276 61</t>
+        </is>
+      </c>
+      <c r="P401" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q401" s="2" t="inlineStr">
+        <is>
+          <t>31377971</t>
+        </is>
+      </c>
+      <c r="R401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/corner-sk-ltd-spol-s-r-o-/</t>
+        </is>
+      </c>
+      <c r="S401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineplanet/</t>
+        </is>
+      </c>
+      <c r="T401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineplanetsk/</t>
+        </is>
+      </c>
+      <c r="U401" s="2" t="inlineStr"/>
+      <c r="V401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/WineplanetVino/</t>
+        </is>
+      </c>
+      <c r="W401" s="2" t="inlineStr">
+        <is>
+          <t>Paulína Letková</t>
+        </is>
+      </c>
+      <c r="X401" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Head of Purchasing Department</t>
+        </is>
+      </c>
+      <c r="Y401" s="2" t="inlineStr"/>
+      <c r="Z401" s="2" t="inlineStr"/>
+      <c r="AA401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paul%C3%ADna-letkov%C3%A1-46a75b2a7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>Corner Sk Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>Corner Sk Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>103152</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>3060/39 Stará Vajnorská</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cornerco.sk, https://wineplanet.sk, https://www.corner.sk</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr"/>
+      <c r="K402" s="2" t="inlineStr"/>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="inlineStr"/>
+      <c r="N402" s="2" t="inlineStr">
+        <is>
+          <t>corner@corner.sk</t>
+        </is>
+      </c>
+      <c r="O402" s="2" t="inlineStr">
+        <is>
+          <t>+421 2455 276 61</t>
+        </is>
+      </c>
+      <c r="P402" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q402" s="2" t="inlineStr">
+        <is>
+          <t>31377971</t>
+        </is>
+      </c>
+      <c r="R402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/corner-sk-ltd-spol-s-r-o-/</t>
+        </is>
+      </c>
+      <c r="S402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineplanet/</t>
+        </is>
+      </c>
+      <c r="T402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineplanetsk/</t>
+        </is>
+      </c>
+      <c r="U402" s="2" t="inlineStr"/>
+      <c r="V402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/WineplanetVino/</t>
+        </is>
+      </c>
+      <c r="W402" s="2" t="inlineStr">
+        <is>
+          <t>Marian Kubis</t>
+        </is>
+      </c>
+      <c r="X402" s="2" t="inlineStr">
+        <is>
+          <t>Executive Sales Director</t>
+        </is>
+      </c>
+      <c r="Y402" s="2" t="inlineStr"/>
+      <c r="Z402" s="2" t="inlineStr"/>
+      <c r="AA402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kubis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>Corner Sk Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>Corner Sk Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>103152</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>3060/39 Stará Vajnorská</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>831 04</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>http://www.cornerco.sk, https://wineplanet.sk, https://www.corner.sk</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr"/>
+      <c r="K403" s="2" t="inlineStr"/>
+      <c r="L403" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M403" s="2" t="inlineStr"/>
+      <c r="N403" s="2" t="inlineStr">
+        <is>
+          <t>corner@corner.sk</t>
+        </is>
+      </c>
+      <c r="O403" s="2" t="inlineStr">
+        <is>
+          <t>+421 2455 276 61</t>
+        </is>
+      </c>
+      <c r="P403" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q403" s="2" t="inlineStr">
+        <is>
+          <t>31377971</t>
+        </is>
+      </c>
+      <c r="R403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/corner-sk-ltd-spol-s-r-o-/</t>
+        </is>
+      </c>
+      <c r="S403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineplanet/</t>
+        </is>
+      </c>
+      <c r="T403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineplanetsk/</t>
+        </is>
+      </c>
+      <c r="U403" s="2" t="inlineStr"/>
+      <c r="V403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/c/WineplanetVino/</t>
+        </is>
+      </c>
+      <c r="W403" s="2" t="inlineStr">
+        <is>
+          <t>Richard Oros</t>
+        </is>
+      </c>
+      <c r="X403" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y403" s="2" t="inlineStr"/>
+      <c r="Z403" s="2" t="inlineStr"/>
+      <c r="AA403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-oros-96903965/</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>Kika Bier, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>Kika Bier, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>19466</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>Žilina</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>Brodno 81</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>010 14</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kikabier.sk</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr"/>
+      <c r="K404" s="2" t="inlineStr"/>
+      <c r="L404" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M404" s="2" t="inlineStr"/>
+      <c r="N404" s="2" t="inlineStr">
+        <is>
+          <t>kikabier@post.sk</t>
+        </is>
+      </c>
+      <c r="O404" s="2" t="inlineStr">
+        <is>
+          <t>+421 41/596 20 70</t>
+        </is>
+      </c>
+      <c r="P404" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q404" s="2" t="inlineStr">
+        <is>
+          <t>36688461</t>
+        </is>
+      </c>
+      <c r="R404" s="2" t="inlineStr"/>
+      <c r="S404" s="2" t="inlineStr"/>
+      <c r="T404" s="2" t="inlineStr"/>
+      <c r="U404" s="2" t="inlineStr"/>
+      <c r="V404" s="2" t="inlineStr"/>
+      <c r="W404" s="2" t="inlineStr"/>
+      <c r="X404" s="2" t="inlineStr"/>
+      <c r="Y404" s="2" t="inlineStr"/>
+      <c r="Z404" s="2" t="inlineStr"/>
+      <c r="AA404" s="2" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>Julk S.r.o.</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>Julk S.r.o.</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>43792</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>Vysoká pri Morave</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Malacky</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>260, 10 Družstevná</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>900 66</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.julk.sk</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr"/>
+      <c r="K405" s="2" t="inlineStr"/>
+      <c r="L405" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M405" s="2" t="inlineStr"/>
+      <c r="N405" s="2" t="inlineStr">
+        <is>
+          <t>office@julk.sk</t>
+        </is>
+      </c>
+      <c r="O405" s="2" t="inlineStr"/>
+      <c r="P405" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q405" s="2" t="inlineStr">
+        <is>
+          <t>47436981</t>
+        </is>
+      </c>
+      <c r="R405" s="2" t="inlineStr"/>
+      <c r="S405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/julk_international_wines/100027452033991/</t>
+        </is>
+      </c>
+      <c r="T405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/julk_international_wines/</t>
+        </is>
+      </c>
+      <c r="U405" s="2" t="inlineStr"/>
+      <c r="V405" s="2" t="inlineStr"/>
+      <c r="W405" s="2" t="inlineStr">
+        <is>
+          <t>Milan Jurík</t>
+        </is>
+      </c>
+      <c r="X405" s="2" t="inlineStr">
+        <is>
+          <t>Sales/ Distribution</t>
+        </is>
+      </c>
+      <c r="Y405" s="2" t="inlineStr"/>
+      <c r="Z405" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA405" s="2" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>Julk S.r.o.</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>Julk S.r.o.</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>43792</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>Vysoká pri Morave</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Malacky</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>260, 10 Družstevná</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>900 66</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.julk.sk</t>
+        </is>
+      </c>
+      <c r="J406" s="2" t="inlineStr"/>
+      <c r="K406" s="2" t="inlineStr"/>
+      <c r="L406" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M406" s="2" t="inlineStr"/>
+      <c r="N406" s="2" t="inlineStr">
+        <is>
+          <t>office@julk.sk</t>
+        </is>
+      </c>
+      <c r="O406" s="2" t="inlineStr"/>
+      <c r="P406" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q406" s="2" t="inlineStr">
+        <is>
+          <t>47436981</t>
+        </is>
+      </c>
+      <c r="R406" s="2" t="inlineStr"/>
+      <c r="S406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/people/julk_international_wines/100027452033991/</t>
+        </is>
+      </c>
+      <c r="T406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/julk_international_wines/</t>
+        </is>
+      </c>
+      <c r="U406" s="2" t="inlineStr"/>
+      <c r="V406" s="2" t="inlineStr"/>
+      <c r="W406" s="2" t="inlineStr">
+        <is>
+          <t>Lukáš Jurík</t>
+        </is>
+      </c>
+      <c r="X406" s="2" t="inlineStr">
+        <is>
+          <t>Consultant For Companies And Gastronomy</t>
+        </is>
+      </c>
+      <c r="Y406" s="2" t="inlineStr"/>
+      <c r="Z406" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA406" s="2" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>Zlatý Vinic S.r.o.</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>Zlatý Vinic S.r.o.</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>53803</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>Banskobystrický kraj</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>23 Zvolenská cesta</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>974 01</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zlatyvinic.eu</t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr"/>
+      <c r="K407" s="2" t="inlineStr"/>
+      <c r="L407" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M407" s="2" t="inlineStr"/>
+      <c r="N407" s="2" t="inlineStr">
+        <is>
+          <t>eshop@zlatyvinic.eu</t>
+        </is>
+      </c>
+      <c r="O407" s="2" t="inlineStr"/>
+      <c r="P407" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q407" s="2" t="inlineStr">
+        <is>
+          <t>36838021</t>
+        </is>
+      </c>
+      <c r="R407" s="2" t="inlineStr"/>
+      <c r="S407" s="2" t="inlineStr"/>
+      <c r="T407" s="2" t="inlineStr"/>
+      <c r="U407" s="2" t="inlineStr"/>
+      <c r="V407" s="2" t="inlineStr"/>
+      <c r="W407" s="2" t="inlineStr"/>
+      <c r="X407" s="2" t="inlineStr"/>
+      <c r="Y407" s="2" t="inlineStr"/>
+      <c r="Z407" s="2" t="inlineStr"/>
+      <c r="AA407" s="2" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>146391</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>2321, 71 Piešťanská</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.sk</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr"/>
+      <c r="K408" s="2" t="inlineStr"/>
+      <c r="L408" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="M408" s="2" t="inlineStr"/>
+      <c r="N408" s="2" t="inlineStr">
+        <is>
+          <t>info@bidfood.sk</t>
+        </is>
+      </c>
+      <c r="O408" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/774 28 11</t>
+        </is>
+      </c>
+      <c r="P408" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q408" s="2" t="inlineStr">
+        <is>
+          <t>34152199</t>
+        </is>
+      </c>
+      <c r="R408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bidfood-slovakia/</t>
+        </is>
+      </c>
+      <c r="S408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfood.sk</t>
+        </is>
+      </c>
+      <c r="T408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfood_slovakia</t>
+        </is>
+      </c>
+      <c r="U408" s="2" t="inlineStr"/>
+      <c r="V408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@bidfoodslovakias.r.o.8178</t>
+        </is>
+      </c>
+      <c r="W408" s="2" t="inlineStr">
+        <is>
+          <t>Tomáš Psota</t>
+        </is>
+      </c>
+      <c r="X408" s="2" t="inlineStr">
+        <is>
+          <t>Purchase Director</t>
+        </is>
+      </c>
+      <c r="Y408" s="2" t="inlineStr"/>
+      <c r="Z408" s="2" t="inlineStr"/>
+      <c r="AA408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tom%C3%A1%C5%A1-psota-20122b295/</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>146391</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>2321, 71 Piešťanská</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.sk</t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="inlineStr"/>
+      <c r="K409" s="2" t="inlineStr"/>
+      <c r="L409" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="M409" s="2" t="inlineStr"/>
+      <c r="N409" s="2" t="inlineStr">
+        <is>
+          <t>info@bidfood.sk</t>
+        </is>
+      </c>
+      <c r="O409" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/774 28 11</t>
+        </is>
+      </c>
+      <c r="P409" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q409" s="2" t="inlineStr">
+        <is>
+          <t>34152199</t>
+        </is>
+      </c>
+      <c r="R409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bidfood-slovakia/</t>
+        </is>
+      </c>
+      <c r="S409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfood.sk</t>
+        </is>
+      </c>
+      <c r="T409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfood_slovakia</t>
+        </is>
+      </c>
+      <c r="U409" s="2" t="inlineStr"/>
+      <c r="V409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@bidfoodslovakias.r.o.8178</t>
+        </is>
+      </c>
+      <c r="W409" s="2" t="inlineStr">
+        <is>
+          <t>Peter Slobodnik</t>
+        </is>
+      </c>
+      <c r="X409" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y409" s="2" t="inlineStr"/>
+      <c r="Z409" s="2" t="inlineStr"/>
+      <c r="AA409" s="2" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>Bidfood Slovakia S. R. O.</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>146391</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>Nové Mesto nad Váhom</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>Trenčiansky kraj</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>2321, 71 Piešťanská</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>915 01</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bidfood.sk</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr"/>
+      <c r="K410" s="2" t="inlineStr"/>
+      <c r="L410" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="M410" s="2" t="inlineStr"/>
+      <c r="N410" s="2" t="inlineStr">
+        <is>
+          <t>info@bidfood.sk</t>
+        </is>
+      </c>
+      <c r="O410" s="2" t="inlineStr">
+        <is>
+          <t>+421 32/774 28 11</t>
+        </is>
+      </c>
+      <c r="P410" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q410" s="2" t="inlineStr">
+        <is>
+          <t>34152199</t>
+        </is>
+      </c>
+      <c r="R410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bidfood-slovakia/</t>
+        </is>
+      </c>
+      <c r="S410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bidfood.sk</t>
+        </is>
+      </c>
+      <c r="T410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bidfood_slovakia</t>
+        </is>
+      </c>
+      <c r="U410" s="2" t="inlineStr"/>
+      <c r="V410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@bidfoodslovakias.r.o.8178</t>
+        </is>
+      </c>
+      <c r="W410" s="2" t="inlineStr">
+        <is>
+          <t>Peter Kadash</t>
+        </is>
+      </c>
+      <c r="X410" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y410" s="2" t="inlineStr"/>
+      <c r="Z410" s="2" t="inlineStr"/>
+      <c r="AA410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-kad%C3%A1%C5%A1-951909147/</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>Coop Jednota Cadca, Spotrebné Družstvo</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>Coop Jednota Cadca, Spotrebné Družstvo</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>146368</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>Čadca</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>87, 32 Palárikova</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>022 01</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>http://www.coopcadca.sk</t>
+        </is>
+      </c>
+      <c r="J411" s="2" t="inlineStr"/>
+      <c r="K411" s="2" t="inlineStr"/>
+      <c r="L411" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="M411" s="2" t="inlineStr"/>
+      <c r="N411" s="2" t="inlineStr">
+        <is>
+          <t>informacie@ca.coop.sk</t>
+        </is>
+      </c>
+      <c r="O411" s="2" t="inlineStr">
+        <is>
+          <t>+421 41/433 21 55</t>
+        </is>
+      </c>
+      <c r="P411" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="Q411" s="2" t="inlineStr">
+        <is>
+          <t>00168947</t>
+        </is>
+      </c>
+      <c r="R411" s="2" t="inlineStr"/>
+      <c r="S411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CJCadca</t>
+        </is>
+      </c>
+      <c r="T411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coop_jednota</t>
+        </is>
+      </c>
+      <c r="U411" s="2" t="inlineStr"/>
+      <c r="V411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@COOPJednotaSlovensko</t>
+        </is>
+      </c>
+      <c r="W411" s="2" t="inlineStr">
+        <is>
+          <t>Miroslav Janík</t>
+        </is>
+      </c>
+      <c r="X411" s="2" t="inlineStr">
+        <is>
+          <t>Chairman Of The Board Of Directors</t>
+        </is>
+      </c>
+      <c r="Y411" s="2" t="inlineStr"/>
+      <c r="Z411" s="2" t="inlineStr"/>
+      <c r="AA411" s="2" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>Coop Jednota Cadca, Spotrebné Družstvo</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>Coop Jednota Cadca, Spotrebné Družstvo</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>146368</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>Čadca</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>Žilinský kraj</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>87, 32 Palárikova</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>022 01</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>http://www.coopcadca.sk</t>
+        </is>
+      </c>
+      <c r="J412" s="2" t="inlineStr"/>
+      <c r="K412" s="2" t="inlineStr"/>
+      <c r="L412" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="inlineStr"/>
+      <c r="N412" s="2" t="inlineStr">
+        <is>
+          <t>informacie@ca.coop.sk</t>
+        </is>
+      </c>
+      <c r="O412" s="2" t="inlineStr">
+        <is>
+          <t>+421 41/433 21 55</t>
+        </is>
+      </c>
+      <c r="P412" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="Q412" s="2" t="inlineStr">
+        <is>
+          <t>00168947</t>
+        </is>
+      </c>
+      <c r="R412" s="2" t="inlineStr"/>
+      <c r="S412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CJCadca</t>
+        </is>
+      </c>
+      <c r="T412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coop_jednota</t>
+        </is>
+      </c>
+      <c r="U412" s="2" t="inlineStr"/>
+      <c r="V412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@COOPJednotaSlovensko</t>
+        </is>
+      </c>
+      <c r="W412" s="2" t="inlineStr">
+        <is>
+          <t>Bohuslav Cyprich</t>
+        </is>
+      </c>
+      <c r="X412" s="2" t="inlineStr">
+        <is>
+          <t>Vice Chairman Of The Board Of Directors</t>
+        </is>
+      </c>
+      <c r="Y412" s="2" t="inlineStr"/>
+      <c r="Z412" s="2" t="inlineStr"/>
+      <c r="AA412" s="2" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>Infotex, Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>Infotex, Spol. S.r.o.</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>24829</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava II</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>8052, 78 Hradská</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>821 07</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr"/>
+      <c r="J413" s="2" t="inlineStr"/>
+      <c r="K413" s="2" t="inlineStr"/>
+      <c r="L413" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M413" s="2" t="inlineStr"/>
+      <c r="N413" s="2" t="inlineStr">
+        <is>
+          <t>info@inmedio.sk</t>
+        </is>
+      </c>
+      <c r="O413" s="2" t="inlineStr"/>
+      <c r="P413" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q413" s="2" t="inlineStr">
+        <is>
+          <t>35753692</t>
+        </is>
+      </c>
+      <c r="R413" s="2" t="inlineStr"/>
+      <c r="S413" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/eshop.inmedio/</t>
+        </is>
+      </c>
+      <c r="T413" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/in_medio/</t>
+        </is>
+      </c>
+      <c r="U413" s="2" t="inlineStr"/>
+      <c r="V413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+      <c r="X413" s="2" t="inlineStr"/>
+      <c r="Y413" s="2" t="inlineStr"/>
+      <c r="Z413" s="2" t="inlineStr"/>
+      <c r="AA413" s="2" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>100yards &amp; Spirits, S.r.o.</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>100yards &amp; Spirits, S.r.o.</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>158583</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>2946, 19 Na Revíne</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>831 01</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinohlad.sk</t>
+        </is>
+      </c>
+      <c r="J414" s="2" t="inlineStr"/>
+      <c r="K414" s="2" t="inlineStr"/>
+      <c r="L414" s="2" t="inlineStr"/>
+      <c r="M414" s="2" t="inlineStr"/>
+      <c r="N414" s="2" t="inlineStr">
+        <is>
+          <t>vyriesime@vinohlad.sk</t>
+        </is>
+      </c>
+      <c r="O414" s="2" t="inlineStr"/>
+      <c r="P414" s="2" t="inlineStr"/>
+      <c r="Q414" s="2" t="inlineStr"/>
+      <c r="R414" s="2" t="inlineStr"/>
+      <c r="S414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinonastanicke/</t>
+        </is>
+      </c>
+      <c r="T414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="inlineStr"/>
+      <c r="V414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+      <c r="X414" s="2" t="inlineStr"/>
+      <c r="Y414" s="2" t="inlineStr"/>
+      <c r="Z414" s="2" t="inlineStr"/>
+      <c r="AA414" s="2" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>Eurotrade Business Services Ltd.</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>Eurotrade Business Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>82260</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>Bratislavský kraj, Bratislava III</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>23 Royova</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>831 01</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>http://www.ebs.sk</t>
+        </is>
+      </c>
+      <c r="J415" s="2" t="inlineStr"/>
+      <c r="K415" s="2" t="inlineStr"/>
+      <c r="L415" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M415" s="2" t="inlineStr"/>
+      <c r="N415" s="2" t="inlineStr">
+        <is>
+          <t>eurotrade@ebs.sk</t>
+        </is>
+      </c>
+      <c r="O415" s="2" t="inlineStr">
+        <is>
+          <t>+421 2/654 571 29</t>
+        </is>
+      </c>
+      <c r="P415" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q415" s="2" t="inlineStr">
+        <is>
+          <t>35866845</t>
+        </is>
+      </c>
+      <c r="R415" s="2" t="inlineStr"/>
+      <c r="S415" s="2" t="inlineStr"/>
+      <c r="T415" s="2" t="inlineStr"/>
+      <c r="U415" s="2" t="inlineStr"/>
+      <c r="V415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr">
+        <is>
+          <t>Juraj Hanus</t>
+        </is>
+      </c>
+      <c r="X415" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y415" s="2" t="inlineStr"/>
+      <c r="Z415" s="2" t="inlineStr"/>
+      <c r="AA415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/juraj-hanus-92716b90/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
